--- a/02 - config/example_big/local_04/agents.xlsx
+++ b/02 - config/example_big/local_04/agents.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1565" uniqueCount="291">
   <si>
     <t>general/agent_id</t>
   </si>
@@ -459,355 +459,352 @@
     <t>meter/prob_missing</t>
   </si>
   <si>
-    <t>CAQ4qbKndqVO5KP</t>
-  </si>
-  <si>
-    <t>P05FuuJKAHoBtll</t>
-  </si>
-  <si>
-    <t>38JpW7PalZEayze</t>
-  </si>
-  <si>
-    <t>OrzVnFyFf8KDWZb</t>
-  </si>
-  <si>
-    <t>0jX330LTbs2R0pg</t>
-  </si>
-  <si>
-    <t>qm3wd3abNgNc06L</t>
-  </si>
-  <si>
-    <t>JbNr6emSGvLnXxr</t>
-  </si>
-  <si>
-    <t>fpCwBkrz7WURF2f</t>
-  </si>
-  <si>
-    <t>mlNdcfxpXKZxCp7</t>
-  </si>
-  <si>
-    <t>bGXeG7MNEBuSaN5</t>
-  </si>
-  <si>
-    <t>hh_3564_0.csv</t>
+    <t>ic5q0vxCICQSPZQ</t>
+  </si>
+  <si>
+    <t>IHH4KqwwrhsT0u2</t>
+  </si>
+  <si>
+    <t>NwB608hYd616bwT</t>
+  </si>
+  <si>
+    <t>VpTHvkEFzN2pvKa</t>
+  </si>
+  <si>
+    <t>SzX0tTKUkNooeVa</t>
+  </si>
+  <si>
+    <t>ApGeebybsEehXkx</t>
+  </si>
+  <si>
+    <t>dLbMR7JDwJmDi8a</t>
+  </si>
+  <si>
+    <t>623EHNw2HEDcL9m</t>
+  </si>
+  <si>
+    <t>AONq6bRKFuMtUUs</t>
+  </si>
+  <si>
+    <t>QRQbVSE6auI6Y0U</t>
+  </si>
+  <si>
+    <t>hh_2532_0.csv</t>
+  </si>
+  <si>
+    <t>hh_2896_0.csv</t>
   </si>
   <si>
     <t>hh_5527_0.csv</t>
   </si>
   <si>
-    <t>hh_2532_0.csv</t>
-  </si>
-  <si>
-    <t>hh_4536_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3648_0.csv</t>
+    <t>hh_3296_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3863_0.csv</t>
+  </si>
+  <si>
+    <t>hh_4402_0.csv</t>
+  </si>
+  <si>
+    <t>naive_average</t>
+  </si>
+  <si>
+    <t>[2, 0, 2, 2, 0, 0, 96, 2, 0, 0, 672]</t>
+  </si>
+  <si>
+    <t>heat_gen_5_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_3_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_5527_0.csv</t>
+  </si>
+  <si>
+    <t>heat_3296_0.csv</t>
+  </si>
+  <si>
+    <t>heat_3863_0.csv</t>
+  </si>
+  <si>
+    <t>heat_4402_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_2_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_4_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_2_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_0_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_5_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_1_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_3_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_6_pu.csv</t>
+  </si>
+  <si>
+    <t>pv_config.json</t>
+  </si>
+  <si>
+    <t>smoothed</t>
+  </si>
+  <si>
+    <t>green_local</t>
+  </si>
+  <si>
+    <t>wind_Siemens_SWT-3.6-130_3600000_130.json</t>
+  </si>
+  <si>
+    <t>wind_Vestas_V117-3.3-MW_3300000_117.json</t>
+  </si>
+  <si>
+    <t>wind_Nordex_MM92_3300000_131.json</t>
+  </si>
+  <si>
+    <t>wind_Senvion-REpower_3.2M122_3200000_122.json</t>
+  </si>
+  <si>
+    <t>weather</t>
+  </si>
+  <si>
+    <t>local</t>
+  </si>
+  <si>
+    <t>ev_fulltime_48.csv</t>
+  </si>
+  <si>
+    <t>ev_parttime_89.csv</t>
+  </si>
+  <si>
+    <t>ev_parttime_90.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_45.csv</t>
+  </si>
+  <si>
+    <t>ev_freetime_3.csv</t>
+  </si>
+  <si>
+    <t>price_sensitive</t>
+  </si>
+  <si>
+    <t>ev_close</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>naive</t>
+  </si>
+  <si>
+    <t>linear</t>
+  </si>
+  <si>
+    <t>general/sub_id</t>
+  </si>
+  <si>
+    <t>general/parameters/apartments_independent</t>
+  </si>
+  <si>
+    <t>general/parameters/apartments</t>
+  </si>
+  <si>
+    <t>caRW7tdL9JZi1Fd</t>
+  </si>
+  <si>
+    <t>unt7uASLERDgKV6</t>
+  </si>
+  <si>
+    <t>main</t>
+  </si>
+  <si>
+    <t>cYlEnPEHWvO5CVW</t>
+  </si>
+  <si>
+    <t>nv2hfAljXDU8FEK</t>
+  </si>
+  <si>
+    <t>SVtbGxViodnYd15</t>
+  </si>
+  <si>
+    <t>iLAqEdxigHsOEsQ</t>
+  </si>
+  <si>
+    <t>BpPvwfFBlqLVDb7</t>
+  </si>
+  <si>
+    <t>hmpUapdYI6xPQBz</t>
+  </si>
+  <si>
+    <t>QPMlqd9Jmqkn3I6</t>
+  </si>
+  <si>
+    <t>Kc2wIWMKcd1Io8r</t>
+  </si>
+  <si>
+    <t>PMQ25lCPiU014uT</t>
+  </si>
+  <si>
+    <t>3qgr1Lyi0fTcYrY</t>
+  </si>
+  <si>
+    <t>rlK6zPUgSnnxW3n</t>
+  </si>
+  <si>
+    <t>UbChkszcM89z0fK</t>
+  </si>
+  <si>
+    <t>qyE1MXusp5Uqu8H</t>
+  </si>
+  <si>
+    <t>Ia0Nagif45cbsSS</t>
+  </si>
+  <si>
+    <t>hh_2262_0.csv</t>
+  </si>
+  <si>
+    <t>hh_1266_0.csv</t>
   </si>
   <si>
     <t>hh_2455_0.csv</t>
   </si>
   <si>
-    <t>naive_average</t>
-  </si>
-  <si>
-    <t>[2, 0, 2, 2, 0, 0, 96, 2, 0, 0, 672]</t>
+    <t>hh_1546_2.csv</t>
+  </si>
+  <si>
+    <t>hh_3125_0.csv</t>
+  </si>
+  <si>
+    <t>hh_913_0.csv</t>
+  </si>
+  <si>
+    <t>hh_2012_3.csv</t>
+  </si>
+  <si>
+    <t>hh_1158_4.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_1_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_0_pu.csv</t>
   </si>
   <si>
     <t>heat_gen_4_pu.csv</t>
   </si>
   <si>
-    <t>heat_5527_0.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_2_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_4536_0.csv</t>
-  </si>
-  <si>
-    <t>heat_3648_0.csv</t>
-  </si>
-  <si>
-    <t>heat_2455_0.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_3_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_5_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_6_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_3_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_0_pu.csv</t>
-  </si>
-  <si>
-    <t>pv_config.json</t>
-  </si>
-  <si>
-    <t>smoothed</t>
-  </si>
-  <si>
-    <t>green_local</t>
-  </si>
-  <si>
-    <t>wind_Nordex_MM92_3300000_131.json</t>
-  </si>
-  <si>
-    <t>wind_Enercon_E-53-800_800000_53.json</t>
-  </si>
-  <si>
-    <t>wind_Enercon_E-101-3500-E2_3500000_101.json</t>
-  </si>
-  <si>
-    <t>weather</t>
-  </si>
-  <si>
-    <t>local</t>
-  </si>
-  <si>
-    <t>ev_fulltime_45.csv</t>
-  </si>
-  <si>
-    <t>ev_parttime_90.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_42.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_43.csv</t>
-  </si>
-  <si>
-    <t>ev_freetime_2.csv</t>
-  </si>
-  <si>
-    <t>price_sensitive</t>
-  </si>
-  <si>
-    <t>ev_close</t>
-  </si>
-  <si>
-    <t>True</t>
-  </si>
-  <si>
-    <t>naive</t>
-  </si>
-  <si>
-    <t>linear</t>
-  </si>
-  <si>
-    <t>general/sub_id</t>
-  </si>
-  <si>
-    <t>general/parameters/apartments_independent</t>
-  </si>
-  <si>
-    <t>general/parameters/apartments</t>
-  </si>
-  <si>
-    <t>fIN6RLaCSLIs34X</t>
-  </si>
-  <si>
-    <t>faG89XBS8LQGBIT</t>
-  </si>
-  <si>
-    <t>main</t>
-  </si>
-  <si>
-    <t>DPpRmoJAzEyUctg</t>
-  </si>
-  <si>
-    <t>eDCcydDkFdMhdg6</t>
-  </si>
-  <si>
-    <t>Zt7eMmbkydw68ro</t>
-  </si>
-  <si>
-    <t>b1bKdSrNn09lvTL</t>
-  </si>
-  <si>
-    <t>WDMMWj3CdvUYmAc</t>
-  </si>
-  <si>
-    <t>Rly2SV5bAywPsti</t>
-  </si>
-  <si>
-    <t>h0EK54BR0dStnX6</t>
-  </si>
-  <si>
-    <t>LWywX8b1UW7qsIv</t>
-  </si>
-  <si>
-    <t>n1aHpiesYKwTEdw</t>
-  </si>
-  <si>
-    <t>GXOwNhY6LN4QB5k</t>
-  </si>
-  <si>
-    <t>mI1HMp7xzXEQPVM</t>
-  </si>
-  <si>
-    <t>ligakxWTagqsUtW</t>
-  </si>
-  <si>
-    <t>2u0caNRWq8dkQXY</t>
-  </si>
-  <si>
-    <t>LLV6xoRvQ98GtrC</t>
-  </si>
-  <si>
-    <t>hh_2262_0.csv</t>
-  </si>
-  <si>
-    <t>hh_1720_0.csv</t>
-  </si>
-  <si>
-    <t>hh_1158_4.csv</t>
-  </si>
-  <si>
-    <t>hh_2687_0.csv</t>
-  </si>
-  <si>
-    <t>hh_1546_2.csv</t>
-  </si>
-  <si>
-    <t>hh_2012_3.csv</t>
-  </si>
-  <si>
-    <t>hh_2896_0.csv</t>
-  </si>
-  <si>
-    <t>hh_945_1.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_0_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_1_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_2_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_4_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_1_pu.csv</t>
-  </si>
-  <si>
     <t>pv_2_pu.csv</t>
   </si>
   <si>
+    <t>pv_1_pu.csv</t>
+  </si>
+  <si>
+    <t>fixed_gen_1_pu.csv</t>
+  </si>
+  <si>
+    <t>ev_parttime_88.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_47.csv</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>_</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>general/parameters/type</t>
+  </si>
+  <si>
+    <t>general/fcast_retraining_frequency</t>
+  </si>
+  <si>
+    <t>uSEpPWgJ3XZ25DE</t>
+  </si>
+  <si>
+    <t>3OMEqBaKVLvA3PZ</t>
+  </si>
+  <si>
+    <t>QWzxH0lBjxJezHE</t>
+  </si>
+  <si>
+    <t>ZAk3BbrgUIKGHje</t>
+  </si>
+  <si>
+    <t>office</t>
+  </si>
+  <si>
+    <t>retail</t>
+  </si>
+  <si>
+    <t>office_pu_0.csv</t>
+  </si>
+  <si>
+    <t>retail_pu_0.csv</t>
+  </si>
+  <si>
+    <t>LvQyvX4XR5Y9Kun</t>
+  </si>
+  <si>
+    <t>MCpgbvD2ttgQ092</t>
+  </si>
+  <si>
+    <t>food</t>
+  </si>
+  <si>
+    <t>tobacco</t>
+  </si>
+  <si>
+    <t>food_pu_0.csv</t>
+  </si>
+  <si>
+    <t>tobacco_pu_0.csv</t>
+  </si>
+  <si>
     <t>pv_3_pu.csv</t>
   </si>
   <si>
-    <t>fixed_gen_1_pu.csv</t>
-  </si>
-  <si>
-    <t>ev_freetime_3.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_49.csv</t>
-  </si>
-  <si>
-    <t>o</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>_</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>general/parameters/type</t>
-  </si>
-  <si>
-    <t>general/fcast_retraining_frequency</t>
-  </si>
-  <si>
-    <t>MiMOLDWdvO8Wy78</t>
-  </si>
-  <si>
-    <t>LmWc11DTOn0d34C</t>
-  </si>
-  <si>
-    <t>pR9hLQSVdZLInjy</t>
-  </si>
-  <si>
-    <t>d6WTzfkMUtlLlDo</t>
-  </si>
-  <si>
-    <t>retail</t>
-  </si>
-  <si>
-    <t>office</t>
-  </si>
-  <si>
-    <t>retail_pu_0.csv</t>
-  </si>
-  <si>
-    <t>office_pu_0.csv</t>
-  </si>
-  <si>
-    <t>pv_1_pu.csv</t>
-  </si>
-  <si>
-    <t>QnFhm1Pv1aaVe0g</t>
-  </si>
-  <si>
-    <t>QOE3HKoozDCq8tw</t>
-  </si>
-  <si>
-    <t>tobacco</t>
-  </si>
-  <si>
-    <t>food</t>
-  </si>
-  <si>
-    <t>tobacco_pu_0.csv</t>
-  </si>
-  <si>
-    <t>food_pu_0.csv</t>
-  </si>
-  <si>
-    <t>wind_Siemens_SWT-3.6-130_3600000_130.json</t>
-  </si>
-  <si>
-    <t>full</t>
-  </si>
-  <si>
-    <t>kWZJYPkjAMgoDTy</t>
-  </si>
-  <si>
-    <t>Xt6DSBzm6ZkFE2b</t>
-  </si>
-  <si>
-    <t>e4NO5d4L5ogT5e1</t>
-  </si>
-  <si>
-    <t>kHfE5aklazt9gY8</t>
-  </si>
-  <si>
-    <t>MbYREwE6tBPw9O8</t>
-  </si>
-  <si>
-    <t>BDhRg5rXQtx9OCW</t>
+    <t>1eYennAPGFlH9Th</t>
+  </si>
+  <si>
+    <t>gCfyAm47XS0WbfL</t>
+  </si>
+  <si>
+    <t>JMTkYh7fvFMSXbf</t>
+  </si>
+  <si>
+    <t>znyd96Yc9GO7QiI</t>
+  </si>
+  <si>
+    <t>NwEkDTs5CsEYAw5</t>
+  </si>
+  <si>
+    <t>cjFNvgMf273J9jV</t>
   </si>
   <si>
     <t>psh/owner</t>
@@ -870,31 +867,31 @@
     <t>hydrogen/quality</t>
   </si>
   <si>
-    <t>VpVR0SQWDVXCpS0</t>
-  </si>
-  <si>
-    <t>sKBLdqZTKGHC4b4</t>
-  </si>
-  <si>
-    <t>PKrckh0Gawj8Y7F</t>
-  </si>
-  <si>
-    <t>Mc1s4lH5J7oAYcD</t>
-  </si>
-  <si>
-    <t>ZnZ0VFZkWBQuGen</t>
-  </si>
-  <si>
-    <t>0UaMMVpfNCH8L0A</t>
-  </si>
-  <si>
-    <t>N7C5Izpti9DJles</t>
-  </si>
-  <si>
-    <t>pLVa3kyoqiBUhUx</t>
-  </si>
-  <si>
-    <t>yAHbtlZFRelcTi6</t>
+    <t>lBLicdaf5xbEfpQ</t>
+  </si>
+  <si>
+    <t>9bD9TCKuliGg9ew</t>
+  </si>
+  <si>
+    <t>VG5qWZbVitYHKaz</t>
+  </si>
+  <si>
+    <t>oMl3cd60m8PxsYn</t>
+  </si>
+  <si>
+    <t>7FrDmqH7kDFcO7M</t>
+  </si>
+  <si>
+    <t>t2NgH5MePjw7QLB</t>
+  </si>
+  <si>
+    <t>fc6FvL5FDBvaqJw</t>
+  </si>
+  <si>
+    <t>9BL69eDM9WWMWdu</t>
+  </si>
+  <si>
+    <t>FZBIBLet74Kc50H</t>
   </si>
 </sst>
 </file>
@@ -1703,10 +1700,10 @@
         <v>146</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -1715,7 +1712,7 @@
         <v>2.6</v>
       </c>
       <c r="J2">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -1730,7 +1727,7 @@
         <v>1</v>
       </c>
       <c r="O2">
-        <v>3564000</v>
+        <v>2532000</v>
       </c>
       <c r="P2" t="s">
         <v>156</v>
@@ -1781,7 +1778,7 @@
         <v>1</v>
       </c>
       <c r="AH2">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="AI2" t="s">
         <v>164</v>
@@ -1847,22 +1844,22 @@
         <v>1</v>
       </c>
       <c r="BD2">
-        <v>5800</v>
+        <v>3900</v>
       </c>
       <c r="BE2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="BF2">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="BG2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BH2" t="b">
         <v>1</v>
       </c>
       <c r="BI2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BJ2">
         <v>2</v>
@@ -1871,19 +1868,28 @@
         <v>9</v>
       </c>
       <c r="BL2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BM2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO2" t="b">
         <v>1</v>
       </c>
+      <c r="BP2">
+        <v>1900</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>181</v>
+      </c>
+      <c r="BR2" t="b">
+        <v>1</v>
+      </c>
       <c r="BS2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="BT2">
         <v>2</v>
@@ -1892,7 +1898,7 @@
         <v>9</v>
       </c>
       <c r="BV2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BW2">
         <v>0</v>
@@ -1904,7 +1910,7 @@
         <v>1</v>
       </c>
       <c r="CC2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CD2">
         <v>2</v>
@@ -1913,7 +1919,7 @@
         <v>9</v>
       </c>
       <c r="CF2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CG2">
         <v>0</v>
@@ -1925,79 +1931,19 @@
         <v>1</v>
       </c>
       <c r="CL2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CM2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CO2" t="b">
         <v>1</v>
       </c>
-      <c r="CP2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CQ2">
-        <v>100000</v>
-      </c>
-      <c r="CR2">
-        <v>25000</v>
-      </c>
-      <c r="CS2">
-        <v>11000</v>
-      </c>
-      <c r="CT2">
-        <v>22000</v>
-      </c>
-      <c r="CU2">
-        <v>200000</v>
-      </c>
-      <c r="CV2">
-        <v>0.9</v>
-      </c>
-      <c r="CW2">
-        <v>0.8</v>
-      </c>
-      <c r="CX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CZ2" t="s">
-        <v>183</v>
-      </c>
-      <c r="DA2">
-        <v>75000</v>
-      </c>
-      <c r="DB2">
-        <v>20000</v>
-      </c>
-      <c r="DC2">
-        <v>7200</v>
-      </c>
-      <c r="DD2">
-        <v>11000</v>
-      </c>
-      <c r="DE2">
-        <v>100000</v>
-      </c>
-      <c r="DF2">
-        <v>0.9</v>
-      </c>
-      <c r="DG2">
-        <v>0.8</v>
-      </c>
-      <c r="DH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="b">
-        <v>0</v>
-      </c>
       <c r="DJ2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="DK2">
         <v>0.05</v>
@@ -2012,10 +1958,10 @@
         <v>8.5</v>
       </c>
       <c r="DO2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DP2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DQ2">
         <v>0</v>
@@ -2024,10 +1970,10 @@
         <v>0</v>
       </c>
       <c r="DS2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="DZ2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EA2">
         <v>0</v>
@@ -2036,28 +1982,28 @@
         <v>0</v>
       </c>
       <c r="EC2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="EH2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EI2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EJ2">
         <v>96</v>
       </c>
       <c r="EK2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EL2">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="EM2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EN2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="EO2">
         <v>0</v>
@@ -2077,10 +2023,10 @@
         <v>147</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -2089,7 +2035,7 @@
         <v>2.6</v>
       </c>
       <c r="J3">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -2104,7 +2050,7 @@
         <v>1</v>
       </c>
       <c r="O3">
-        <v>5527000</v>
+        <v>2896000</v>
       </c>
       <c r="P3" t="s">
         <v>157</v>
@@ -2155,13 +2101,13 @@
         <v>1</v>
       </c>
       <c r="AH3">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="AI3" t="s">
         <v>165</v>
       </c>
       <c r="AJ3">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AK3" t="s">
         <v>162</v>
@@ -2188,7 +2134,7 @@
         <v>1</v>
       </c>
       <c r="AS3">
-        <v>2400000</v>
+        <v>3200000</v>
       </c>
       <c r="AT3" t="s">
         <v>172</v>
@@ -2212,16 +2158,31 @@
         <v>90</v>
       </c>
       <c r="BA3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC3" t="b">
         <v>1</v>
       </c>
+      <c r="BD3">
+        <v>3900</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>178</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BG3">
+        <v>40</v>
+      </c>
+      <c r="BH3" t="b">
+        <v>1</v>
+      </c>
       <c r="BI3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BJ3">
         <v>2</v>
@@ -2230,7 +2191,7 @@
         <v>9</v>
       </c>
       <c r="BL3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BM3">
         <v>0</v>
@@ -2242,7 +2203,7 @@
         <v>1</v>
       </c>
       <c r="BS3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="BT3">
         <v>2</v>
@@ -2251,7 +2212,7 @@
         <v>9</v>
       </c>
       <c r="BV3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BW3">
         <v>0</v>
@@ -2263,7 +2224,7 @@
         <v>1</v>
       </c>
       <c r="CC3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CD3">
         <v>2</v>
@@ -2272,7 +2233,7 @@
         <v>9</v>
       </c>
       <c r="CF3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CG3">
         <v>0</v>
@@ -2284,19 +2245,49 @@
         <v>1</v>
       </c>
       <c r="CL3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CM3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO3" t="b">
         <v>1</v>
       </c>
+      <c r="CP3" t="s">
+        <v>187</v>
+      </c>
+      <c r="CQ3">
+        <v>75000</v>
+      </c>
+      <c r="CR3">
+        <v>20000</v>
+      </c>
+      <c r="CS3">
+        <v>7200</v>
+      </c>
+      <c r="CT3">
+        <v>11000</v>
+      </c>
+      <c r="CU3">
+        <v>100000</v>
+      </c>
+      <c r="CV3">
+        <v>0.9</v>
+      </c>
+      <c r="CW3">
+        <v>0.8</v>
+      </c>
+      <c r="CX3" t="b">
+        <v>0</v>
+      </c>
+      <c r="CY3" t="b">
+        <v>0</v>
+      </c>
       <c r="DJ3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="DK3">
         <v>0.05</v>
@@ -2311,22 +2302,40 @@
         <v>8.5</v>
       </c>
       <c r="DO3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DP3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DQ3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS3" t="s">
-        <v>190</v>
+        <v>194</v>
+      </c>
+      <c r="DT3">
+        <v>2900</v>
+      </c>
+      <c r="DU3">
+        <v>2900</v>
+      </c>
+      <c r="DV3">
+        <v>0.95</v>
+      </c>
+      <c r="DW3">
+        <v>0.1</v>
+      </c>
+      <c r="DX3" t="b">
+        <v>0</v>
+      </c>
+      <c r="DY3" t="b">
+        <v>0</v>
       </c>
       <c r="DZ3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EA3">
         <v>0</v>
@@ -2335,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="EC3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="EH3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EI3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EJ3">
         <v>96</v>
       </c>
       <c r="EK3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EL3">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="EM3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EN3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="EO3">
         <v>0</v>
@@ -2403,7 +2412,7 @@
         <v>1</v>
       </c>
       <c r="O4">
-        <v>2532000</v>
+        <v>5527000</v>
       </c>
       <c r="P4" t="s">
         <v>158</v>
@@ -2460,7 +2469,7 @@
         <v>166</v>
       </c>
       <c r="AJ4">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AK4" t="s">
         <v>162</v>
@@ -2487,10 +2496,10 @@
         <v>1</v>
       </c>
       <c r="AS4">
-        <v>1800000</v>
+        <v>2100000</v>
       </c>
       <c r="AT4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AU4">
         <v>55</v>
@@ -2520,10 +2529,10 @@
         <v>1</v>
       </c>
       <c r="BD4">
-        <v>3600</v>
+        <v>7200</v>
       </c>
       <c r="BE4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="BF4">
         <v>0</v>
@@ -2535,7 +2544,7 @@
         <v>1</v>
       </c>
       <c r="BI4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BJ4">
         <v>2</v>
@@ -2544,28 +2553,19 @@
         <v>9</v>
       </c>
       <c r="BL4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BM4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="b">
         <v>1</v>
       </c>
-      <c r="BP4">
-        <v>2100</v>
-      </c>
-      <c r="BQ4" t="s">
-        <v>178</v>
-      </c>
-      <c r="BR4" t="b">
-        <v>1</v>
-      </c>
       <c r="BS4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="BT4">
         <v>2</v>
@@ -2574,7 +2574,7 @@
         <v>9</v>
       </c>
       <c r="BV4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BW4">
         <v>0</v>
@@ -2586,7 +2586,7 @@
         <v>1</v>
       </c>
       <c r="CC4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CD4">
         <v>2</v>
@@ -2595,7 +2595,7 @@
         <v>9</v>
       </c>
       <c r="CF4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CG4">
         <v>0</v>
@@ -2607,49 +2607,19 @@
         <v>1</v>
       </c>
       <c r="CL4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CM4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO4" t="b">
         <v>1</v>
       </c>
-      <c r="CP4" t="s">
-        <v>184</v>
-      </c>
-      <c r="CQ4">
-        <v>50000</v>
-      </c>
-      <c r="CR4">
-        <v>15000</v>
-      </c>
-      <c r="CS4">
-        <v>7200</v>
-      </c>
-      <c r="CT4">
-        <v>7200</v>
-      </c>
-      <c r="CU4">
-        <v>50000</v>
-      </c>
-      <c r="CV4">
-        <v>0.9</v>
-      </c>
-      <c r="CW4">
-        <v>0.8</v>
-      </c>
-      <c r="CX4" t="b">
-        <v>0</v>
-      </c>
-      <c r="CY4" t="b">
-        <v>0</v>
-      </c>
       <c r="DJ4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="DK4">
         <v>0.05</v>
@@ -2664,10 +2634,10 @@
         <v>8.5</v>
       </c>
       <c r="DO4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DP4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DQ4">
         <v>1</v>
@@ -2676,13 +2646,13 @@
         <v>1</v>
       </c>
       <c r="DS4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="DT4">
-        <v>2500</v>
+        <v>5500</v>
       </c>
       <c r="DU4">
-        <v>2500</v>
+        <v>5500</v>
       </c>
       <c r="DV4">
         <v>0.95</v>
@@ -2697,7 +2667,7 @@
         <v>0</v>
       </c>
       <c r="DZ4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EA4">
         <v>0</v>
@@ -2706,28 +2676,28 @@
         <v>0</v>
       </c>
       <c r="EC4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="EH4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EI4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EJ4">
         <v>96</v>
       </c>
       <c r="EK4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EL4">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="EM4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EN4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="EO4">
         <v>0</v>
@@ -2774,7 +2744,7 @@
         <v>1</v>
       </c>
       <c r="O5">
-        <v>4536000</v>
+        <v>3296000</v>
       </c>
       <c r="P5" t="s">
         <v>159</v>
@@ -2831,7 +2801,7 @@
         <v>167</v>
       </c>
       <c r="AJ5">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AK5" t="s">
         <v>162</v>
@@ -2891,22 +2861,22 @@
         <v>1</v>
       </c>
       <c r="BD5">
-        <v>6400</v>
+        <v>5200</v>
       </c>
       <c r="BE5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="BF5">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="BG5">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BH5" t="b">
         <v>1</v>
       </c>
       <c r="BI5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BJ5">
         <v>2</v>
@@ -2915,50 +2885,41 @@
         <v>9</v>
       </c>
       <c r="BL5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BM5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="b">
         <v>1</v>
       </c>
-      <c r="BP5">
-        <v>3100</v>
-      </c>
-      <c r="BQ5" t="s">
+      <c r="BS5" t="s">
+        <v>185</v>
+      </c>
+      <c r="BT5">
+        <v>2</v>
+      </c>
+      <c r="BU5">
+        <v>9</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>180</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="b">
+        <v>1</v>
+      </c>
+      <c r="CC5" t="s">
         <v>179</v>
       </c>
-      <c r="BR5" t="b">
-        <v>1</v>
-      </c>
-      <c r="BS5" t="s">
-        <v>181</v>
-      </c>
-      <c r="BT5">
-        <v>2</v>
-      </c>
-      <c r="BU5">
-        <v>9</v>
-      </c>
-      <c r="BV5" t="s">
-        <v>177</v>
-      </c>
-      <c r="BW5">
-        <v>0</v>
-      </c>
-      <c r="BX5">
-        <v>0</v>
-      </c>
-      <c r="BY5" t="b">
-        <v>1</v>
-      </c>
-      <c r="CC5" t="s">
-        <v>176</v>
-      </c>
       <c r="CD5">
         <v>2</v>
       </c>
@@ -2966,7 +2927,7 @@
         <v>9</v>
       </c>
       <c r="CF5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CG5">
         <v>0</v>
@@ -2978,7 +2939,7 @@
         <v>1</v>
       </c>
       <c r="CL5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CM5">
         <v>0</v>
@@ -2990,7 +2951,7 @@
         <v>1</v>
       </c>
       <c r="DJ5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="DK5">
         <v>0.05</v>
@@ -3005,10 +2966,10 @@
         <v>8.5</v>
       </c>
       <c r="DO5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DP5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DQ5">
         <v>0</v>
@@ -3017,10 +2978,10 @@
         <v>0</v>
       </c>
       <c r="DS5" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="DZ5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EA5">
         <v>0</v>
@@ -3029,28 +2990,28 @@
         <v>0</v>
       </c>
       <c r="EC5" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="EH5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EI5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EJ5">
         <v>96</v>
       </c>
       <c r="EK5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EL5">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="EM5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EN5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="EO5">
         <v>0</v>
@@ -3070,10 +3031,10 @@
         <v>150</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -3082,7 +3043,7 @@
         <v>2.6</v>
       </c>
       <c r="J6">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -3100,7 +3061,7 @@
         <v>5527000</v>
       </c>
       <c r="P6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q6" t="s">
         <v>162</v>
@@ -3148,10 +3109,10 @@
         <v>1</v>
       </c>
       <c r="AH6">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="AI6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AJ6">
         <v>55</v>
@@ -3181,10 +3142,10 @@
         <v>1</v>
       </c>
       <c r="AS6">
-        <v>3200000</v>
+        <v>2100000</v>
       </c>
       <c r="AT6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AU6">
         <v>55</v>
@@ -3205,16 +3166,31 @@
         <v>90</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC6" t="b">
         <v>1</v>
       </c>
+      <c r="BD6">
+        <v>7200</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>178</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>40</v>
+      </c>
+      <c r="BH6" t="b">
+        <v>1</v>
+      </c>
       <c r="BI6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BJ6">
         <v>2</v>
@@ -3223,19 +3199,28 @@
         <v>9</v>
       </c>
       <c r="BL6" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO6" t="b">
         <v>1</v>
       </c>
+      <c r="BP6">
+        <v>2300</v>
+      </c>
+      <c r="BQ6" t="s">
+        <v>181</v>
+      </c>
+      <c r="BR6" t="b">
+        <v>1</v>
+      </c>
       <c r="BS6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="BT6">
         <v>2</v>
@@ -3244,7 +3229,7 @@
         <v>9</v>
       </c>
       <c r="BV6" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BW6">
         <v>0</v>
@@ -3256,7 +3241,7 @@
         <v>1</v>
       </c>
       <c r="CC6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CD6">
         <v>2</v>
@@ -3265,7 +3250,7 @@
         <v>9</v>
       </c>
       <c r="CF6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CG6">
         <v>0</v>
@@ -3277,7 +3262,7 @@
         <v>1</v>
       </c>
       <c r="CL6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CM6">
         <v>1</v>
@@ -3289,22 +3274,22 @@
         <v>1</v>
       </c>
       <c r="CP6" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="CQ6">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="CR6">
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="CS6">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="CT6">
-        <v>7200</v>
+        <v>22000</v>
       </c>
       <c r="CU6">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="CV6">
         <v>0.9</v>
@@ -3319,7 +3304,7 @@
         <v>0</v>
       </c>
       <c r="DJ6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="DK6">
         <v>0.05</v>
@@ -3334,22 +3319,40 @@
         <v>8.5</v>
       </c>
       <c r="DO6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DP6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DQ6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS6" t="s">
-        <v>190</v>
+        <v>194</v>
+      </c>
+      <c r="DT6">
+        <v>5500</v>
+      </c>
+      <c r="DU6">
+        <v>5500</v>
+      </c>
+      <c r="DV6">
+        <v>0.95</v>
+      </c>
+      <c r="DW6">
+        <v>0.1</v>
+      </c>
+      <c r="DX6" t="b">
+        <v>0</v>
+      </c>
+      <c r="DY6" t="b">
+        <v>0</v>
       </c>
       <c r="DZ6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EA6">
         <v>0</v>
@@ -3358,28 +3361,28 @@
         <v>0</v>
       </c>
       <c r="EC6" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="EH6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EI6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EJ6">
         <v>96</v>
       </c>
       <c r="EK6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EL6">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="EM6" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EN6">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="EO6">
         <v>0</v>
@@ -3399,10 +3402,10 @@
         <v>151</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -3411,7 +3414,7 @@
         <v>2.6</v>
       </c>
       <c r="J7">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -3426,7 +3429,7 @@
         <v>1</v>
       </c>
       <c r="O7">
-        <v>3648000</v>
+        <v>3863000</v>
       </c>
       <c r="P7" t="s">
         <v>160</v>
@@ -3477,13 +3480,13 @@
         <v>1</v>
       </c>
       <c r="AH7">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="AI7" t="s">
         <v>168</v>
       </c>
       <c r="AJ7">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AK7" t="s">
         <v>162</v>
@@ -3510,10 +3513,10 @@
         <v>1</v>
       </c>
       <c r="AS7">
-        <v>2800000</v>
+        <v>2100000</v>
       </c>
       <c r="AT7" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="AU7">
         <v>55</v>
@@ -3543,10 +3546,10 @@
         <v>1</v>
       </c>
       <c r="BD7">
-        <v>5000</v>
+        <v>6500</v>
       </c>
       <c r="BE7" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="BF7">
         <v>-20</v>
@@ -3558,7 +3561,7 @@
         <v>1</v>
       </c>
       <c r="BI7" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BJ7">
         <v>2</v>
@@ -3567,19 +3570,28 @@
         <v>9</v>
       </c>
       <c r="BL7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO7" t="b">
         <v>1</v>
       </c>
+      <c r="BP7">
+        <v>2800</v>
+      </c>
+      <c r="BQ7" t="s">
+        <v>182</v>
+      </c>
+      <c r="BR7" t="b">
+        <v>1</v>
+      </c>
       <c r="BS7" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="BT7">
         <v>2</v>
@@ -3588,7 +3600,7 @@
         <v>9</v>
       </c>
       <c r="BV7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BW7">
         <v>0</v>
@@ -3600,7 +3612,7 @@
         <v>1</v>
       </c>
       <c r="CC7" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CD7">
         <v>2</v>
@@ -3609,7 +3621,7 @@
         <v>9</v>
       </c>
       <c r="CF7" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CG7">
         <v>0</v>
@@ -3621,19 +3633,49 @@
         <v>1</v>
       </c>
       <c r="CL7" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CM7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO7" t="b">
         <v>1</v>
       </c>
+      <c r="CP7" t="s">
+        <v>189</v>
+      </c>
+      <c r="CQ7">
+        <v>50000</v>
+      </c>
+      <c r="CR7">
+        <v>15000</v>
+      </c>
+      <c r="CS7">
+        <v>7200</v>
+      </c>
+      <c r="CT7">
+        <v>7200</v>
+      </c>
+      <c r="CU7">
+        <v>50000</v>
+      </c>
+      <c r="CV7">
+        <v>0.9</v>
+      </c>
+      <c r="CW7">
+        <v>0.8</v>
+      </c>
+      <c r="CX7" t="b">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="b">
+        <v>0</v>
+      </c>
       <c r="DJ7" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="DK7">
         <v>0.05</v>
@@ -3648,10 +3690,10 @@
         <v>8.5</v>
       </c>
       <c r="DO7" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DP7" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DQ7">
         <v>1</v>
@@ -3660,13 +3702,13 @@
         <v>1</v>
       </c>
       <c r="DS7" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="DT7">
-        <v>3600</v>
+        <v>3900</v>
       </c>
       <c r="DU7">
-        <v>3600</v>
+        <v>3900</v>
       </c>
       <c r="DV7">
         <v>0.95</v>
@@ -3681,7 +3723,7 @@
         <v>0</v>
       </c>
       <c r="DZ7" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EA7">
         <v>0</v>
@@ -3690,28 +3732,28 @@
         <v>0</v>
       </c>
       <c r="EC7" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="EH7" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EI7" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EJ7">
         <v>96</v>
       </c>
       <c r="EK7" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EL7">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="EM7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EN7">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="EO7">
         <v>0</v>
@@ -3731,10 +3773,10 @@
         <v>152</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -3743,7 +3785,7 @@
         <v>2.6</v>
       </c>
       <c r="J8">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -3758,10 +3800,10 @@
         <v>1</v>
       </c>
       <c r="O8">
-        <v>2455000</v>
+        <v>3296000</v>
       </c>
       <c r="P8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Q8" t="s">
         <v>162</v>
@@ -3809,10 +3851,10 @@
         <v>1</v>
       </c>
       <c r="AH8">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="AI8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AJ8">
         <v>55</v>
@@ -3842,10 +3884,10 @@
         <v>1</v>
       </c>
       <c r="AS8">
-        <v>2800000</v>
+        <v>1800000</v>
       </c>
       <c r="AT8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AU8">
         <v>55</v>
@@ -3866,31 +3908,16 @@
         <v>90</v>
       </c>
       <c r="BA8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="b">
         <v>1</v>
       </c>
-      <c r="BD8">
-        <v>3500</v>
-      </c>
-      <c r="BE8" t="s">
-        <v>175</v>
-      </c>
-      <c r="BF8">
-        <v>0</v>
-      </c>
-      <c r="BG8">
-        <v>40</v>
-      </c>
-      <c r="BH8" t="b">
-        <v>1</v>
-      </c>
       <c r="BI8" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BJ8">
         <v>2</v>
@@ -3899,7 +3926,7 @@
         <v>9</v>
       </c>
       <c r="BL8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BM8">
         <v>1</v>
@@ -3911,16 +3938,16 @@
         <v>1</v>
       </c>
       <c r="BP8">
-        <v>1400</v>
+        <v>2100</v>
       </c>
       <c r="BQ8" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="BR8" t="b">
         <v>1</v>
       </c>
       <c r="BS8" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="BT8">
         <v>2</v>
@@ -3929,7 +3956,7 @@
         <v>9</v>
       </c>
       <c r="BV8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BW8">
         <v>0</v>
@@ -3941,7 +3968,7 @@
         <v>1</v>
       </c>
       <c r="CC8" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CD8">
         <v>2</v>
@@ -3950,7 +3977,7 @@
         <v>9</v>
       </c>
       <c r="CF8" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CG8">
         <v>0</v>
@@ -3962,19 +3989,49 @@
         <v>1</v>
       </c>
       <c r="CL8" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CM8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO8" t="b">
         <v>1</v>
       </c>
+      <c r="CP8" t="s">
+        <v>190</v>
+      </c>
+      <c r="CQ8">
+        <v>50000</v>
+      </c>
+      <c r="CR8">
+        <v>15000</v>
+      </c>
+      <c r="CS8">
+        <v>7200</v>
+      </c>
+      <c r="CT8">
+        <v>7200</v>
+      </c>
+      <c r="CU8">
+        <v>50000</v>
+      </c>
+      <c r="CV8">
+        <v>0.9</v>
+      </c>
+      <c r="CW8">
+        <v>0.8</v>
+      </c>
+      <c r="CX8" t="b">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="b">
+        <v>0</v>
+      </c>
       <c r="DJ8" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="DK8">
         <v>0.05</v>
@@ -3989,40 +4046,22 @@
         <v>8.5</v>
       </c>
       <c r="DO8" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DP8" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DQ8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS8" t="s">
-        <v>190</v>
-      </c>
-      <c r="DT8">
-        <v>2500</v>
-      </c>
-      <c r="DU8">
-        <v>2500</v>
-      </c>
-      <c r="DV8">
-        <v>0.95</v>
-      </c>
-      <c r="DW8">
-        <v>0.1</v>
-      </c>
-      <c r="DX8" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY8" t="b">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="DZ8" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EA8">
         <v>0</v>
@@ -4031,25 +4070,25 @@
         <v>0</v>
       </c>
       <c r="EC8" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="EH8" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EI8" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EJ8">
         <v>96</v>
       </c>
       <c r="EK8" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EL8">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="EM8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EN8">
         <v>10</v>
@@ -4072,10 +4111,10 @@
         <v>153</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>2</v>
@@ -4084,7 +4123,7 @@
         <v>2.6</v>
       </c>
       <c r="J9">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -4099,10 +4138,10 @@
         <v>1</v>
       </c>
       <c r="O9">
-        <v>4536000</v>
+        <v>4402000</v>
       </c>
       <c r="P9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q9" t="s">
         <v>162</v>
@@ -4150,13 +4189,13 @@
         <v>1</v>
       </c>
       <c r="AH9">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="AI9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AJ9">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AK9" t="s">
         <v>162</v>
@@ -4186,7 +4225,7 @@
         <v>2400000</v>
       </c>
       <c r="AT9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AU9">
         <v>55</v>
@@ -4207,31 +4246,16 @@
         <v>90</v>
       </c>
       <c r="BA9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="b">
         <v>1</v>
       </c>
-      <c r="BD9">
-        <v>6200</v>
-      </c>
-      <c r="BE9" t="s">
-        <v>175</v>
-      </c>
-      <c r="BF9">
-        <v>0</v>
-      </c>
-      <c r="BG9">
-        <v>40</v>
-      </c>
-      <c r="BH9" t="b">
-        <v>1</v>
-      </c>
       <c r="BI9" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BJ9">
         <v>2</v>
@@ -4240,7 +4264,7 @@
         <v>9</v>
       </c>
       <c r="BL9" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BM9">
         <v>1</v>
@@ -4252,26 +4276,26 @@
         <v>1</v>
       </c>
       <c r="BP9">
-        <v>3300</v>
+        <v>3000</v>
       </c>
       <c r="BQ9" t="s">
+        <v>184</v>
+      </c>
+      <c r="BR9" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS9" t="s">
+        <v>185</v>
+      </c>
+      <c r="BT9">
+        <v>2</v>
+      </c>
+      <c r="BU9">
+        <v>9</v>
+      </c>
+      <c r="BV9" t="s">
         <v>180</v>
       </c>
-      <c r="BR9" t="b">
-        <v>1</v>
-      </c>
-      <c r="BS9" t="s">
-        <v>181</v>
-      </c>
-      <c r="BT9">
-        <v>2</v>
-      </c>
-      <c r="BU9">
-        <v>9</v>
-      </c>
-      <c r="BV9" t="s">
-        <v>177</v>
-      </c>
       <c r="BW9">
         <v>0</v>
       </c>
@@ -4282,7 +4306,7 @@
         <v>1</v>
       </c>
       <c r="CC9" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CD9">
         <v>2</v>
@@ -4291,7 +4315,7 @@
         <v>9</v>
       </c>
       <c r="CF9" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CG9">
         <v>0</v>
@@ -4303,7 +4327,7 @@
         <v>1</v>
       </c>
       <c r="CL9" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CM9">
         <v>1</v>
@@ -4315,7 +4339,7 @@
         <v>1</v>
       </c>
       <c r="CP9" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="CQ9">
         <v>75000</v>
@@ -4345,7 +4369,7 @@
         <v>0</v>
       </c>
       <c r="DJ9" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="DK9">
         <v>0.05</v>
@@ -4360,40 +4384,22 @@
         <v>8.5</v>
       </c>
       <c r="DO9" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DP9" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DQ9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS9" t="s">
-        <v>190</v>
-      </c>
-      <c r="DT9">
-        <v>4500</v>
-      </c>
-      <c r="DU9">
-        <v>4500</v>
-      </c>
-      <c r="DV9">
-        <v>0.95</v>
-      </c>
-      <c r="DW9">
-        <v>0.1</v>
-      </c>
-      <c r="DX9" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY9" t="b">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="DZ9" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EA9">
         <v>0</v>
@@ -4402,25 +4408,25 @@
         <v>0</v>
       </c>
       <c r="EC9" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="EH9" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EI9" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EJ9">
         <v>96</v>
       </c>
       <c r="EK9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EL9">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="EM9" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EN9">
         <v>10</v>
@@ -4443,10 +4449,10 @@
         <v>154</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -4455,7 +4461,7 @@
         <v>2.6</v>
       </c>
       <c r="J10">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -4470,10 +4476,10 @@
         <v>1</v>
       </c>
       <c r="O10">
-        <v>4536000</v>
+        <v>4402000</v>
       </c>
       <c r="P10" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q10" t="s">
         <v>162</v>
@@ -4521,7 +4527,7 @@
         <v>1</v>
       </c>
       <c r="AH10">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="AI10" t="s">
         <v>170</v>
@@ -4554,10 +4560,10 @@
         <v>1</v>
       </c>
       <c r="AS10">
-        <v>2100000</v>
+        <v>2800000</v>
       </c>
       <c r="AT10" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="AU10">
         <v>55</v>
@@ -4587,10 +4593,10 @@
         <v>1</v>
       </c>
       <c r="BD10">
-        <v>5800</v>
+        <v>6200</v>
       </c>
       <c r="BE10" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="BF10">
         <v>0</v>
@@ -4602,7 +4608,7 @@
         <v>1</v>
       </c>
       <c r="BI10" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BJ10">
         <v>2</v>
@@ -4611,50 +4617,41 @@
         <v>9</v>
       </c>
       <c r="BL10" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BM10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO10" t="b">
         <v>1</v>
       </c>
-      <c r="BP10">
-        <v>2400</v>
-      </c>
-      <c r="BQ10" t="s">
+      <c r="BS10" t="s">
+        <v>185</v>
+      </c>
+      <c r="BT10">
+        <v>2</v>
+      </c>
+      <c r="BU10">
+        <v>9</v>
+      </c>
+      <c r="BV10" t="s">
+        <v>180</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="b">
+        <v>1</v>
+      </c>
+      <c r="CC10" t="s">
         <v>179</v>
       </c>
-      <c r="BR10" t="b">
-        <v>1</v>
-      </c>
-      <c r="BS10" t="s">
-        <v>181</v>
-      </c>
-      <c r="BT10">
-        <v>2</v>
-      </c>
-      <c r="BU10">
-        <v>9</v>
-      </c>
-      <c r="BV10" t="s">
-        <v>177</v>
-      </c>
-      <c r="BW10">
-        <v>0</v>
-      </c>
-      <c r="BX10">
-        <v>0</v>
-      </c>
-      <c r="BY10" t="b">
-        <v>1</v>
-      </c>
-      <c r="CC10" t="s">
-        <v>176</v>
-      </c>
       <c r="CD10">
         <v>2</v>
       </c>
@@ -4662,7 +4659,7 @@
         <v>9</v>
       </c>
       <c r="CF10" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CG10">
         <v>0</v>
@@ -4674,7 +4671,7 @@
         <v>1</v>
       </c>
       <c r="CL10" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CM10">
         <v>0</v>
@@ -4686,7 +4683,7 @@
         <v>1</v>
       </c>
       <c r="DJ10" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="DK10">
         <v>0.05</v>
@@ -4701,10 +4698,10 @@
         <v>8.5</v>
       </c>
       <c r="DO10" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DP10" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DQ10">
         <v>1</v>
@@ -4713,13 +4710,13 @@
         <v>1</v>
       </c>
       <c r="DS10" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="DT10">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="DU10">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="DV10">
         <v>0.95</v>
@@ -4734,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="DZ10" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EA10">
         <v>0</v>
@@ -4743,28 +4740,28 @@
         <v>0</v>
       </c>
       <c r="EC10" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="EH10" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EI10" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EJ10">
         <v>96</v>
       </c>
       <c r="EK10" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EL10">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="EM10" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EN10">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="EO10">
         <v>0</v>
@@ -4784,10 +4781,10 @@
         <v>155</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -4796,7 +4793,7 @@
         <v>2.6</v>
       </c>
       <c r="J11">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -4811,10 +4808,10 @@
         <v>1</v>
       </c>
       <c r="O11">
-        <v>3648000</v>
+        <v>4402000</v>
       </c>
       <c r="P11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q11" t="s">
         <v>162</v>
@@ -4862,13 +4859,13 @@
         <v>1</v>
       </c>
       <c r="AH11">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="AI11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ11">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AK11" t="s">
         <v>162</v>
@@ -4895,10 +4892,10 @@
         <v>1</v>
       </c>
       <c r="AS11">
-        <v>2100000</v>
+        <v>3200000</v>
       </c>
       <c r="AT11" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="AU11">
         <v>55</v>
@@ -4928,10 +4925,10 @@
         <v>1</v>
       </c>
       <c r="BD11">
-        <v>6300</v>
+        <v>7300</v>
       </c>
       <c r="BE11" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="BF11">
         <v>0</v>
@@ -4943,7 +4940,7 @@
         <v>1</v>
       </c>
       <c r="BI11" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BJ11">
         <v>2</v>
@@ -4952,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="BL11" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BM11">
         <v>0</v>
@@ -4964,7 +4961,7 @@
         <v>1</v>
       </c>
       <c r="BS11" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="BT11">
         <v>2</v>
@@ -4973,7 +4970,7 @@
         <v>9</v>
       </c>
       <c r="BV11" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BW11">
         <v>0</v>
@@ -4985,7 +4982,7 @@
         <v>1</v>
       </c>
       <c r="CC11" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CD11">
         <v>2</v>
@@ -4994,7 +4991,7 @@
         <v>9</v>
       </c>
       <c r="CF11" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CG11">
         <v>0</v>
@@ -5006,49 +5003,19 @@
         <v>1</v>
       </c>
       <c r="CL11" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CM11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO11" t="b">
         <v>1</v>
       </c>
-      <c r="CP11" t="s">
-        <v>187</v>
-      </c>
-      <c r="CQ11">
-        <v>75000</v>
-      </c>
-      <c r="CR11">
-        <v>20000</v>
-      </c>
-      <c r="CS11">
-        <v>7200</v>
-      </c>
-      <c r="CT11">
-        <v>11000</v>
-      </c>
-      <c r="CU11">
-        <v>100000</v>
-      </c>
-      <c r="CV11">
-        <v>0.9</v>
-      </c>
-      <c r="CW11">
-        <v>0.8</v>
-      </c>
-      <c r="CX11" t="b">
-        <v>0</v>
-      </c>
-      <c r="CY11" t="b">
-        <v>0</v>
-      </c>
       <c r="DJ11" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="DK11">
         <v>0.05</v>
@@ -5063,10 +5030,10 @@
         <v>8.5</v>
       </c>
       <c r="DO11" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DP11" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DQ11">
         <v>1</v>
@@ -5075,13 +5042,13 @@
         <v>1</v>
       </c>
       <c r="DS11" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="DT11">
-        <v>3600</v>
+        <v>4400</v>
       </c>
       <c r="DU11">
-        <v>3600</v>
+        <v>4400</v>
       </c>
       <c r="DV11">
         <v>0.95</v>
@@ -5096,7 +5063,7 @@
         <v>0</v>
       </c>
       <c r="DZ11" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EA11">
         <v>0</v>
@@ -5105,28 +5072,28 @@
         <v>0</v>
       </c>
       <c r="EC11" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="EH11" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EI11" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EJ11">
         <v>96</v>
       </c>
       <c r="EK11" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EL11">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="EM11" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EN11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="EO11">
         <v>0</v>
@@ -5162,13 +5129,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -5602,10 +5569,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
@@ -5641,7 +5608,7 @@
         <v>1</v>
       </c>
       <c r="R2">
-        <v>11635000</v>
+        <v>13210000</v>
       </c>
       <c r="T2" t="s">
         <v>162</v>
@@ -5740,10 +5707,10 @@
         <v>1</v>
       </c>
       <c r="BG2">
-        <v>17000</v>
+        <v>20000</v>
       </c>
       <c r="BH2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="BI2">
         <v>0</v>
@@ -5755,7 +5722,7 @@
         <v>1</v>
       </c>
       <c r="BL2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BM2">
         <v>2</v>
@@ -5764,38 +5731,29 @@
         <v>9</v>
       </c>
       <c r="BO2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BP2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="b">
         <v>1</v>
       </c>
-      <c r="BS2">
-        <v>8400</v>
-      </c>
-      <c r="BT2" t="s">
+      <c r="BV2" t="s">
+        <v>185</v>
+      </c>
+      <c r="BW2">
+        <v>2</v>
+      </c>
+      <c r="BX2">
+        <v>9</v>
+      </c>
+      <c r="BY2" t="s">
         <v>180</v>
       </c>
-      <c r="BU2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BV2" t="s">
-        <v>181</v>
-      </c>
-      <c r="BW2">
-        <v>2</v>
-      </c>
-      <c r="BX2">
-        <v>9</v>
-      </c>
-      <c r="BY2" t="s">
-        <v>177</v>
-      </c>
       <c r="BZ2">
         <v>1</v>
       </c>
@@ -5806,16 +5764,16 @@
         <v>1</v>
       </c>
       <c r="CC2">
-        <v>1900</v>
+        <v>2600</v>
       </c>
       <c r="CD2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="CE2" t="b">
         <v>0</v>
       </c>
       <c r="CF2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CG2">
         <v>2</v>
@@ -5824,7 +5782,7 @@
         <v>9</v>
       </c>
       <c r="CI2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CJ2">
         <v>0</v>
@@ -5836,7 +5794,7 @@
         <v>1</v>
       </c>
       <c r="CO2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CP2">
         <v>0</v>
@@ -5848,10 +5806,10 @@
         <v>1</v>
       </c>
       <c r="DR2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DT2">
         <v>1</v>
@@ -5863,10 +5821,10 @@
         <v>1</v>
       </c>
       <c r="DW2">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="DX2">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="DY2">
         <v>0.95</v>
@@ -5881,7 +5839,7 @@
         <v>0</v>
       </c>
       <c r="EC2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="ED2">
         <v>1</v>
@@ -5905,25 +5863,25 @@
         <v>0.1</v>
       </c>
       <c r="EK2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EL2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM2">
         <v>96</v>
       </c>
       <c r="EN2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO2">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="EP2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EQ2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="ER2">
         <v>0</v>
@@ -5940,10 +5898,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
@@ -5982,7 +5940,7 @@
         <v>2262000</v>
       </c>
       <c r="S3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="T3" t="s">
         <v>162</v>
@@ -6030,7 +5988,7 @@
         <v>3850000</v>
       </c>
       <c r="AL3" t="s">
-        <v>164</v>
+        <v>225</v>
       </c>
       <c r="AM3">
         <v>55</v>
@@ -6060,10 +6018,10 @@
         <v>1</v>
       </c>
       <c r="AV3">
-        <v>2400</v>
+        <v>2100</v>
       </c>
       <c r="AW3" t="s">
-        <v>223</v>
+        <v>177</v>
       </c>
       <c r="AX3">
         <v>55</v>
@@ -6093,7 +6051,7 @@
         <v>1</v>
       </c>
       <c r="BL3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BM3">
         <v>2</v>
@@ -6102,7 +6060,7 @@
         <v>9</v>
       </c>
       <c r="BO3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BP3">
         <v>0</v>
@@ -6114,7 +6072,7 @@
         <v>1</v>
       </c>
       <c r="BV3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="BW3">
         <v>2</v>
@@ -6123,7 +6081,7 @@
         <v>9</v>
       </c>
       <c r="BY3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -6135,7 +6093,7 @@
         <v>1</v>
       </c>
       <c r="CF3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CG3">
         <v>2</v>
@@ -6144,7 +6102,7 @@
         <v>9</v>
       </c>
       <c r="CI3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CJ3">
         <v>0</v>
@@ -6156,7 +6114,7 @@
         <v>1</v>
       </c>
       <c r="CO3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CP3">
         <v>0</v>
@@ -6168,7 +6126,7 @@
         <v>1</v>
       </c>
       <c r="DM3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="DN3">
         <v>0.05</v>
@@ -6183,10 +6141,10 @@
         <v>8</v>
       </c>
       <c r="DR3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DT3">
         <v>0</v>
@@ -6198,7 +6156,7 @@
         <v>1</v>
       </c>
       <c r="EC3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="ED3">
         <v>0</v>
@@ -6210,25 +6168,25 @@
         <v>1</v>
       </c>
       <c r="EK3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EL3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM3">
         <v>96</v>
       </c>
       <c r="EN3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO3">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="EP3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EQ3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="ER3">
         <v>0</v>
@@ -6245,10 +6203,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F4" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G4" t="b">
         <v>0</v>
@@ -6284,10 +6242,10 @@
         <v>1</v>
       </c>
       <c r="R4">
-        <v>1720000</v>
+        <v>2262000</v>
       </c>
       <c r="S4" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="T4" t="s">
         <v>162</v>
@@ -6365,10 +6323,10 @@
         <v>1</v>
       </c>
       <c r="AV4">
-        <v>2100</v>
+        <v>2400</v>
       </c>
       <c r="AW4" t="s">
-        <v>223</v>
+        <v>177</v>
       </c>
       <c r="AX4">
         <v>55</v>
@@ -6398,7 +6356,7 @@
         <v>1</v>
       </c>
       <c r="BL4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BM4">
         <v>2</v>
@@ -6407,7 +6365,7 @@
         <v>9</v>
       </c>
       <c r="BO4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BP4">
         <v>0</v>
@@ -6419,7 +6377,7 @@
         <v>1</v>
       </c>
       <c r="BV4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="BW4">
         <v>2</v>
@@ -6428,7 +6386,7 @@
         <v>9</v>
       </c>
       <c r="BY4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -6440,7 +6398,7 @@
         <v>1</v>
       </c>
       <c r="CF4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CG4">
         <v>2</v>
@@ -6449,7 +6407,7 @@
         <v>9</v>
       </c>
       <c r="CI4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CJ4">
         <v>0</v>
@@ -6461,49 +6419,19 @@
         <v>1</v>
       </c>
       <c r="CO4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CP4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR4" t="b">
         <v>1</v>
       </c>
-      <c r="CS4" t="s">
-        <v>184</v>
-      </c>
-      <c r="CT4">
-        <v>50000</v>
-      </c>
-      <c r="CU4">
-        <v>15000</v>
-      </c>
-      <c r="CV4">
-        <v>7200</v>
-      </c>
-      <c r="CW4">
-        <v>7200</v>
-      </c>
-      <c r="CX4">
-        <v>50000</v>
-      </c>
-      <c r="CY4">
-        <v>0.9</v>
-      </c>
-      <c r="CZ4">
-        <v>0.8</v>
-      </c>
-      <c r="DA4" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB4" t="b">
-        <v>0</v>
-      </c>
       <c r="DM4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="DN4">
         <v>0.05</v>
@@ -6518,10 +6446,10 @@
         <v>8</v>
       </c>
       <c r="DR4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DT4">
         <v>0</v>
@@ -6533,7 +6461,7 @@
         <v>1</v>
       </c>
       <c r="EC4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="ED4">
         <v>0</v>
@@ -6545,25 +6473,25 @@
         <v>1</v>
       </c>
       <c r="EK4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EL4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM4">
         <v>96</v>
       </c>
       <c r="EN4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO4">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="EP4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EQ4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="ER4">
         <v>0</v>
@@ -6580,10 +6508,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F5" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
@@ -6622,7 +6550,7 @@
         <v>2262000</v>
       </c>
       <c r="S5" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="T5" t="s">
         <v>162</v>
@@ -6670,7 +6598,7 @@
         <v>3850000</v>
       </c>
       <c r="AL5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AM5">
         <v>35</v>
@@ -6700,10 +6628,10 @@
         <v>1</v>
       </c>
       <c r="AV5">
-        <v>2400</v>
+        <v>1800</v>
       </c>
       <c r="AW5" t="s">
-        <v>224</v>
+        <v>172</v>
       </c>
       <c r="AX5">
         <v>55</v>
@@ -6733,7 +6661,7 @@
         <v>1</v>
       </c>
       <c r="BL5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BM5">
         <v>2</v>
@@ -6742,7 +6670,7 @@
         <v>9</v>
       </c>
       <c r="BO5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BP5">
         <v>0</v>
@@ -6754,7 +6682,7 @@
         <v>1</v>
       </c>
       <c r="BV5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="BW5">
         <v>2</v>
@@ -6763,7 +6691,7 @@
         <v>9</v>
       </c>
       <c r="BY5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -6775,7 +6703,7 @@
         <v>1</v>
       </c>
       <c r="CF5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CG5">
         <v>2</v>
@@ -6784,7 +6712,7 @@
         <v>9</v>
       </c>
       <c r="CI5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CJ5">
         <v>0</v>
@@ -6796,7 +6724,7 @@
         <v>1</v>
       </c>
       <c r="CO5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CP5">
         <v>0</v>
@@ -6808,7 +6736,7 @@
         <v>1</v>
       </c>
       <c r="DM5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="DN5">
         <v>0.05</v>
@@ -6823,10 +6751,10 @@
         <v>8</v>
       </c>
       <c r="DR5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DT5">
         <v>0</v>
@@ -6838,7 +6766,7 @@
         <v>1</v>
       </c>
       <c r="EC5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="ED5">
         <v>0</v>
@@ -6850,25 +6778,25 @@
         <v>1</v>
       </c>
       <c r="EK5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EL5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM5">
         <v>96</v>
       </c>
       <c r="EN5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO5">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="EP5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EQ5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="ER5">
         <v>0</v>
@@ -6885,10 +6813,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F6" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -6924,10 +6852,10 @@
         <v>1</v>
       </c>
       <c r="R6">
-        <v>1158000</v>
+        <v>1266000</v>
       </c>
       <c r="S6" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="T6" t="s">
         <v>162</v>
@@ -6975,10 +6903,10 @@
         <v>3850000</v>
       </c>
       <c r="AL6" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AM6">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AN6" t="s">
         <v>162</v>
@@ -7008,7 +6936,7 @@
         <v>1800</v>
       </c>
       <c r="AW6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AX6">
         <v>55</v>
@@ -7038,7 +6966,7 @@
         <v>1</v>
       </c>
       <c r="BL6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BM6">
         <v>2</v>
@@ -7047,7 +6975,7 @@
         <v>9</v>
       </c>
       <c r="BO6" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BP6">
         <v>0</v>
@@ -7059,7 +6987,7 @@
         <v>1</v>
       </c>
       <c r="BV6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="BW6">
         <v>2</v>
@@ -7068,7 +6996,7 @@
         <v>9</v>
       </c>
       <c r="BY6" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -7080,7 +7008,7 @@
         <v>1</v>
       </c>
       <c r="CF6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CG6">
         <v>2</v>
@@ -7089,7 +7017,7 @@
         <v>9</v>
       </c>
       <c r="CI6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CJ6">
         <v>0</v>
@@ -7101,46 +7029,16 @@
         <v>1</v>
       </c>
       <c r="CO6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CP6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR6" t="b">
         <v>1</v>
-      </c>
-      <c r="CS6" t="s">
-        <v>229</v>
-      </c>
-      <c r="CT6">
-        <v>75000</v>
-      </c>
-      <c r="CU6">
-        <v>20000</v>
-      </c>
-      <c r="CV6">
-        <v>7200</v>
-      </c>
-      <c r="CW6">
-        <v>11000</v>
-      </c>
-      <c r="CX6">
-        <v>100000</v>
-      </c>
-      <c r="CY6">
-        <v>0.9</v>
-      </c>
-      <c r="CZ6">
-        <v>0.8</v>
-      </c>
-      <c r="DA6" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB6" t="b">
-        <v>0</v>
       </c>
       <c r="DM6" t="s">
         <v>234</v>
@@ -7158,10 +7056,10 @@
         <v>8</v>
       </c>
       <c r="DR6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DT6">
         <v>0</v>
@@ -7173,7 +7071,7 @@
         <v>1</v>
       </c>
       <c r="EC6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="ED6">
         <v>0</v>
@@ -7185,22 +7083,22 @@
         <v>1</v>
       </c>
       <c r="EK6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EL6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM6">
         <v>96</v>
       </c>
       <c r="EN6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO6">
         <v>48</v>
       </c>
       <c r="EP6" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EQ6">
         <v>30</v>
@@ -7220,10 +7118,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F7" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -7259,10 +7157,10 @@
         <v>1</v>
       </c>
       <c r="R7">
-        <v>2687000</v>
+        <v>2262000</v>
       </c>
       <c r="S7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="T7" t="s">
         <v>162</v>
@@ -7310,7 +7208,7 @@
         <v>3850000</v>
       </c>
       <c r="AL7" t="s">
-        <v>222</v>
+        <v>164</v>
       </c>
       <c r="AM7">
         <v>55</v>
@@ -7340,10 +7238,10 @@
         <v>1</v>
       </c>
       <c r="AV7">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="AW7" t="s">
-        <v>223</v>
+        <v>177</v>
       </c>
       <c r="AX7">
         <v>55</v>
@@ -7373,7 +7271,7 @@
         <v>1</v>
       </c>
       <c r="BL7" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BM7">
         <v>2</v>
@@ -7382,7 +7280,7 @@
         <v>9</v>
       </c>
       <c r="BO7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BP7">
         <v>0</v>
@@ -7394,7 +7292,7 @@
         <v>1</v>
       </c>
       <c r="BV7" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="BW7">
         <v>2</v>
@@ -7403,7 +7301,7 @@
         <v>9</v>
       </c>
       <c r="BY7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -7415,7 +7313,7 @@
         <v>1</v>
       </c>
       <c r="CF7" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CG7">
         <v>2</v>
@@ -7424,7 +7322,7 @@
         <v>9</v>
       </c>
       <c r="CI7" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CJ7">
         <v>0</v>
@@ -7436,7 +7334,7 @@
         <v>1</v>
       </c>
       <c r="CO7" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CP7">
         <v>0</v>
@@ -7463,10 +7361,10 @@
         <v>8</v>
       </c>
       <c r="DR7" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS7" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DT7">
         <v>0</v>
@@ -7478,7 +7376,7 @@
         <v>1</v>
       </c>
       <c r="EC7" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="ED7">
         <v>0</v>
@@ -7490,25 +7388,25 @@
         <v>1</v>
       </c>
       <c r="EK7" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EL7" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM7">
         <v>96</v>
       </c>
       <c r="EN7" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO7">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="EP7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EQ7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="ER7">
         <v>0</v>
@@ -7525,10 +7423,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F8" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
@@ -7564,10 +7462,10 @@
         <v>1</v>
       </c>
       <c r="R8">
-        <v>1546000</v>
+        <v>2896000</v>
       </c>
       <c r="S8" t="s">
-        <v>217</v>
+        <v>157</v>
       </c>
       <c r="T8" t="s">
         <v>162</v>
@@ -7615,10 +7513,10 @@
         <v>3850000</v>
       </c>
       <c r="AL8" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="AM8">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AN8" t="s">
         <v>162</v>
@@ -7648,7 +7546,7 @@
         <v>2100</v>
       </c>
       <c r="AW8" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AX8">
         <v>55</v>
@@ -7678,7 +7576,7 @@
         <v>1</v>
       </c>
       <c r="BL8" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BM8">
         <v>2</v>
@@ -7687,7 +7585,7 @@
         <v>9</v>
       </c>
       <c r="BO8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BP8">
         <v>0</v>
@@ -7699,7 +7597,7 @@
         <v>1</v>
       </c>
       <c r="BV8" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="BW8">
         <v>2</v>
@@ -7708,7 +7606,7 @@
         <v>9</v>
       </c>
       <c r="BY8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -7720,7 +7618,7 @@
         <v>1</v>
       </c>
       <c r="CF8" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CG8">
         <v>2</v>
@@ -7729,7 +7627,7 @@
         <v>9</v>
       </c>
       <c r="CI8" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CJ8">
         <v>0</v>
@@ -7741,16 +7639,76 @@
         <v>1</v>
       </c>
       <c r="CO8" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CP8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CR8" t="b">
         <v>1</v>
+      </c>
+      <c r="CS8" t="s">
+        <v>231</v>
+      </c>
+      <c r="CT8">
+        <v>75000</v>
+      </c>
+      <c r="CU8">
+        <v>20000</v>
+      </c>
+      <c r="CV8">
+        <v>7200</v>
+      </c>
+      <c r="CW8">
+        <v>11000</v>
+      </c>
+      <c r="CX8">
+        <v>100000</v>
+      </c>
+      <c r="CY8">
+        <v>0.9</v>
+      </c>
+      <c r="CZ8">
+        <v>0.8</v>
+      </c>
+      <c r="DA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="b">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="s">
+        <v>187</v>
+      </c>
+      <c r="DD8">
+        <v>50000</v>
+      </c>
+      <c r="DE8">
+        <v>15000</v>
+      </c>
+      <c r="DF8">
+        <v>7200</v>
+      </c>
+      <c r="DG8">
+        <v>7200</v>
+      </c>
+      <c r="DH8">
+        <v>50000</v>
+      </c>
+      <c r="DI8">
+        <v>0.9</v>
+      </c>
+      <c r="DJ8">
+        <v>0.8</v>
+      </c>
+      <c r="DK8" t="b">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="b">
+        <v>0</v>
       </c>
       <c r="DM8" t="s">
         <v>235</v>
@@ -7768,10 +7726,10 @@
         <v>8</v>
       </c>
       <c r="DR8" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS8" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DT8">
         <v>0</v>
@@ -7783,7 +7741,7 @@
         <v>1</v>
       </c>
       <c r="EC8" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="ED8">
         <v>0</v>
@@ -7795,25 +7753,25 @@
         <v>1</v>
       </c>
       <c r="EK8" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EL8" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM8">
         <v>96</v>
       </c>
       <c r="EN8" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO8">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="EP8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EQ8">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="ER8">
         <v>0</v>
@@ -7830,10 +7788,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F9" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -7869,7 +7827,7 @@
         <v>1</v>
       </c>
       <c r="R9">
-        <v>14531000</v>
+        <v>15926000</v>
       </c>
       <c r="T9" t="s">
         <v>162</v>
@@ -7941,7 +7899,7 @@
         <v>1</v>
       </c>
       <c r="AV9">
-        <v>22400</v>
+        <v>22800</v>
       </c>
       <c r="AY9" t="s">
         <v>162</v>
@@ -7968,10 +7926,10 @@
         <v>1</v>
       </c>
       <c r="BG9">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="BH9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="BI9">
         <v>0</v>
@@ -7983,7 +7941,7 @@
         <v>1</v>
       </c>
       <c r="BL9" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BM9">
         <v>2</v>
@@ -7992,19 +7950,28 @@
         <v>9</v>
       </c>
       <c r="BO9" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR9" t="b">
         <v>1</v>
       </c>
+      <c r="BS9">
+        <v>13000</v>
+      </c>
+      <c r="BT9" t="s">
+        <v>184</v>
+      </c>
+      <c r="BU9" t="b">
+        <v>1</v>
+      </c>
       <c r="BV9" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="BW9">
         <v>2</v>
@@ -8013,7 +7980,7 @@
         <v>9</v>
       </c>
       <c r="BY9" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BZ9">
         <v>1</v>
@@ -8025,16 +7992,16 @@
         <v>1</v>
       </c>
       <c r="CC9">
-        <v>1600</v>
+        <v>2800</v>
       </c>
       <c r="CD9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="CE9" t="b">
         <v>0</v>
       </c>
       <c r="CF9" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CG9">
         <v>2</v>
@@ -8043,7 +8010,7 @@
         <v>9</v>
       </c>
       <c r="CI9" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CJ9">
         <v>0</v>
@@ -8055,7 +8022,7 @@
         <v>1</v>
       </c>
       <c r="CO9" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CP9">
         <v>0</v>
@@ -8067,10 +8034,10 @@
         <v>1</v>
       </c>
       <c r="DR9" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS9" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DT9">
         <v>1</v>
@@ -8082,10 +8049,10 @@
         <v>1</v>
       </c>
       <c r="DW9">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="DX9">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="DY9">
         <v>0.95</v>
@@ -8100,7 +8067,7 @@
         <v>0</v>
       </c>
       <c r="EC9" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="ED9">
         <v>1</v>
@@ -8124,22 +8091,22 @@
         <v>0.1</v>
       </c>
       <c r="EK9" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EL9" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM9">
         <v>96</v>
       </c>
       <c r="EN9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO9">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="EP9" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EQ9">
         <v>0</v>
@@ -8159,10 +8126,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F10" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
@@ -8198,10 +8165,10 @@
         <v>1</v>
       </c>
       <c r="R10">
-        <v>2455000</v>
+        <v>2262000</v>
       </c>
       <c r="S10" t="s">
-        <v>161</v>
+        <v>217</v>
       </c>
       <c r="T10" t="s">
         <v>162</v>
@@ -8249,7 +8216,7 @@
         <v>15000000</v>
       </c>
       <c r="AL10" t="s">
-        <v>166</v>
+        <v>225</v>
       </c>
       <c r="AM10">
         <v>55</v>
@@ -8282,7 +8249,7 @@
         <v>2800</v>
       </c>
       <c r="AW10" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="AX10">
         <v>55</v>
@@ -8312,7 +8279,7 @@
         <v>1</v>
       </c>
       <c r="BL10" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BM10">
         <v>2</v>
@@ -8321,7 +8288,7 @@
         <v>9</v>
       </c>
       <c r="BO10" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BP10">
         <v>0</v>
@@ -8333,7 +8300,7 @@
         <v>1</v>
       </c>
       <c r="BV10" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="BW10">
         <v>2</v>
@@ -8342,7 +8309,7 @@
         <v>9</v>
       </c>
       <c r="BY10" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -8354,7 +8321,7 @@
         <v>1</v>
       </c>
       <c r="CF10" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CG10">
         <v>2</v>
@@ -8363,7 +8330,7 @@
         <v>9</v>
       </c>
       <c r="CI10" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CJ10">
         <v>0</v>
@@ -8375,7 +8342,7 @@
         <v>1</v>
       </c>
       <c r="CO10" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CP10">
         <v>0</v>
@@ -8387,7 +8354,7 @@
         <v>1</v>
       </c>
       <c r="DM10" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="DN10">
         <v>0.05</v>
@@ -8402,10 +8369,10 @@
         <v>8</v>
       </c>
       <c r="DR10" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS10" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DT10">
         <v>0</v>
@@ -8417,7 +8384,7 @@
         <v>1</v>
       </c>
       <c r="EC10" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="ED10">
         <v>0</v>
@@ -8429,22 +8396,22 @@
         <v>1</v>
       </c>
       <c r="EK10" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EL10" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM10">
         <v>96</v>
       </c>
       <c r="EN10" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO10">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="EP10" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EQ10">
         <v>10</v>
@@ -8464,10 +8431,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F11" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G11" t="b">
         <v>0</v>
@@ -8503,10 +8470,10 @@
         <v>1</v>
       </c>
       <c r="R11">
-        <v>1546000</v>
+        <v>2455000</v>
       </c>
       <c r="S11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="T11" t="s">
         <v>162</v>
@@ -8554,7 +8521,7 @@
         <v>15000000</v>
       </c>
       <c r="AL11" t="s">
-        <v>221</v>
+        <v>170</v>
       </c>
       <c r="AM11">
         <v>35</v>
@@ -8584,10 +8551,10 @@
         <v>1</v>
       </c>
       <c r="AV11">
-        <v>3200</v>
+        <v>2800</v>
       </c>
       <c r="AW11" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="AX11">
         <v>55</v>
@@ -8617,7 +8584,7 @@
         <v>1</v>
       </c>
       <c r="BL11" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BM11">
         <v>2</v>
@@ -8626,7 +8593,7 @@
         <v>9</v>
       </c>
       <c r="BO11" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BP11">
         <v>0</v>
@@ -8638,7 +8605,7 @@
         <v>1</v>
       </c>
       <c r="BV11" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="BW11">
         <v>2</v>
@@ -8647,7 +8614,7 @@
         <v>9</v>
       </c>
       <c r="BY11" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -8659,7 +8626,7 @@
         <v>1</v>
       </c>
       <c r="CF11" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CG11">
         <v>2</v>
@@ -8668,7 +8635,7 @@
         <v>9</v>
       </c>
       <c r="CI11" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CJ11">
         <v>0</v>
@@ -8680,49 +8647,19 @@
         <v>1</v>
       </c>
       <c r="CO11" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CP11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR11" t="b">
         <v>1</v>
       </c>
-      <c r="CS11" t="s">
-        <v>229</v>
-      </c>
-      <c r="CT11">
-        <v>50000</v>
-      </c>
-      <c r="CU11">
-        <v>15000</v>
-      </c>
-      <c r="CV11">
-        <v>7200</v>
-      </c>
-      <c r="CW11">
-        <v>7200</v>
-      </c>
-      <c r="CX11">
-        <v>50000</v>
-      </c>
-      <c r="CY11">
-        <v>0.9</v>
-      </c>
-      <c r="CZ11">
-        <v>0.8</v>
-      </c>
-      <c r="DA11" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB11" t="b">
-        <v>0</v>
-      </c>
       <c r="DM11" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="DN11">
         <v>0.05</v>
@@ -8737,10 +8674,10 @@
         <v>8</v>
       </c>
       <c r="DR11" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS11" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DT11">
         <v>0</v>
@@ -8752,7 +8689,7 @@
         <v>1</v>
       </c>
       <c r="EC11" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="ED11">
         <v>0</v>
@@ -8764,22 +8701,22 @@
         <v>1</v>
       </c>
       <c r="EK11" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EL11" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM11">
         <v>96</v>
       </c>
       <c r="EN11" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO11">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="EP11" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EQ11">
         <v>30</v>
@@ -8799,10 +8736,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F12" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="G12" t="b">
         <v>0</v>
@@ -8838,10 +8775,10 @@
         <v>1</v>
       </c>
       <c r="R12">
-        <v>2012000</v>
+        <v>1546000</v>
       </c>
       <c r="S12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="T12" t="s">
         <v>162</v>
@@ -8889,7 +8826,7 @@
         <v>15000000</v>
       </c>
       <c r="AL12" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="AM12">
         <v>55</v>
@@ -8919,10 +8856,10 @@
         <v>1</v>
       </c>
       <c r="AV12">
-        <v>2400</v>
+        <v>2800</v>
       </c>
       <c r="AW12" t="s">
-        <v>224</v>
+        <v>171</v>
       </c>
       <c r="AX12">
         <v>55</v>
@@ -8952,7 +8889,7 @@
         <v>1</v>
       </c>
       <c r="BL12" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BM12">
         <v>2</v>
@@ -8961,7 +8898,7 @@
         <v>9</v>
       </c>
       <c r="BO12" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BP12">
         <v>0</v>
@@ -8973,7 +8910,7 @@
         <v>1</v>
       </c>
       <c r="BV12" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="BW12">
         <v>2</v>
@@ -8982,7 +8919,7 @@
         <v>9</v>
       </c>
       <c r="BY12" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -8994,7 +8931,7 @@
         <v>1</v>
       </c>
       <c r="CF12" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CG12">
         <v>2</v>
@@ -9003,7 +8940,7 @@
         <v>9</v>
       </c>
       <c r="CI12" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CJ12">
         <v>0</v>
@@ -9015,7 +8952,7 @@
         <v>1</v>
       </c>
       <c r="CO12" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CP12">
         <v>0</v>
@@ -9027,7 +8964,7 @@
         <v>1</v>
       </c>
       <c r="DM12" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="DN12">
         <v>0.05</v>
@@ -9042,10 +8979,10 @@
         <v>8</v>
       </c>
       <c r="DR12" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS12" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DT12">
         <v>0</v>
@@ -9057,7 +8994,7 @@
         <v>1</v>
       </c>
       <c r="EC12" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="ED12">
         <v>0</v>
@@ -9069,25 +9006,25 @@
         <v>1</v>
       </c>
       <c r="EK12" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EL12" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM12">
         <v>96</v>
       </c>
       <c r="EN12" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO12">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="EP12" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EQ12">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="ER12">
         <v>0</v>
@@ -9104,10 +9041,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F13" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="G13" t="b">
         <v>0</v>
@@ -9143,10 +9080,10 @@
         <v>1</v>
       </c>
       <c r="R13">
-        <v>2896000</v>
+        <v>3125000</v>
       </c>
       <c r="S13" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="T13" t="s">
         <v>162</v>
@@ -9194,10 +9131,10 @@
         <v>15000000</v>
       </c>
       <c r="AL13" t="s">
-        <v>221</v>
+        <v>164</v>
       </c>
       <c r="AM13">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AN13" t="s">
         <v>162</v>
@@ -9224,10 +9161,10 @@
         <v>1</v>
       </c>
       <c r="AV13">
-        <v>2400</v>
+        <v>3200</v>
       </c>
       <c r="AW13" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AX13">
         <v>55</v>
@@ -9257,7 +9194,7 @@
         <v>1</v>
       </c>
       <c r="BL13" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BM13">
         <v>2</v>
@@ -9266,7 +9203,7 @@
         <v>9</v>
       </c>
       <c r="BO13" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BP13">
         <v>0</v>
@@ -9278,7 +9215,7 @@
         <v>1</v>
       </c>
       <c r="BV13" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="BW13">
         <v>2</v>
@@ -9287,7 +9224,7 @@
         <v>9</v>
       </c>
       <c r="BY13" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -9299,7 +9236,7 @@
         <v>1</v>
       </c>
       <c r="CF13" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CG13">
         <v>2</v>
@@ -9308,7 +9245,7 @@
         <v>9</v>
       </c>
       <c r="CI13" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CJ13">
         <v>0</v>
@@ -9320,19 +9257,49 @@
         <v>1</v>
       </c>
       <c r="CO13" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CP13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CR13" t="b">
         <v>1</v>
       </c>
+      <c r="CS13" t="s">
+        <v>188</v>
+      </c>
+      <c r="CT13">
+        <v>50000</v>
+      </c>
+      <c r="CU13">
+        <v>15000</v>
+      </c>
+      <c r="CV13">
+        <v>7200</v>
+      </c>
+      <c r="CW13">
+        <v>7200</v>
+      </c>
+      <c r="CX13">
+        <v>50000</v>
+      </c>
+      <c r="CY13">
+        <v>0.9</v>
+      </c>
+      <c r="CZ13">
+        <v>0.8</v>
+      </c>
+      <c r="DA13" t="b">
+        <v>0</v>
+      </c>
+      <c r="DB13" t="b">
+        <v>0</v>
+      </c>
       <c r="DM13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="DN13">
         <v>0.05</v>
@@ -9347,10 +9314,10 @@
         <v>8</v>
       </c>
       <c r="DR13" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS13" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DT13">
         <v>0</v>
@@ -9362,7 +9329,7 @@
         <v>1</v>
       </c>
       <c r="EC13" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="ED13">
         <v>0</v>
@@ -9374,22 +9341,22 @@
         <v>1</v>
       </c>
       <c r="EK13" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EL13" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM13">
         <v>96</v>
       </c>
       <c r="EN13" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO13">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="EP13" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EQ13">
         <v>0</v>
@@ -9409,10 +9376,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F14" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G14" t="b">
         <v>0</v>
@@ -9448,10 +9415,10 @@
         <v>1</v>
       </c>
       <c r="R14">
-        <v>945000</v>
+        <v>913000</v>
       </c>
       <c r="S14" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="T14" t="s">
         <v>162</v>
@@ -9499,10 +9466,10 @@
         <v>15000000</v>
       </c>
       <c r="AL14" t="s">
-        <v>221</v>
+        <v>164</v>
       </c>
       <c r="AM14">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AN14" t="s">
         <v>162</v>
@@ -9529,10 +9496,10 @@
         <v>1</v>
       </c>
       <c r="AV14">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="AW14" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
       <c r="AX14">
         <v>55</v>
@@ -9562,7 +9529,7 @@
         <v>1</v>
       </c>
       <c r="BL14" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BM14">
         <v>2</v>
@@ -9571,7 +9538,7 @@
         <v>9</v>
       </c>
       <c r="BO14" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BP14">
         <v>0</v>
@@ -9583,7 +9550,7 @@
         <v>1</v>
       </c>
       <c r="BV14" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="BW14">
         <v>2</v>
@@ -9592,7 +9559,7 @@
         <v>9</v>
       </c>
       <c r="BY14" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -9604,7 +9571,7 @@
         <v>1</v>
       </c>
       <c r="CF14" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CG14">
         <v>2</v>
@@ -9613,7 +9580,7 @@
         <v>9</v>
       </c>
       <c r="CI14" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CJ14">
         <v>0</v>
@@ -9625,7 +9592,7 @@
         <v>1</v>
       </c>
       <c r="CO14" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CP14">
         <v>0</v>
@@ -9637,7 +9604,7 @@
         <v>1</v>
       </c>
       <c r="DM14" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="DN14">
         <v>0.05</v>
@@ -9652,10 +9619,10 @@
         <v>8</v>
       </c>
       <c r="DR14" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS14" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DT14">
         <v>0</v>
@@ -9667,7 +9634,7 @@
         <v>1</v>
       </c>
       <c r="EC14" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="ED14">
         <v>0</v>
@@ -9679,25 +9646,25 @@
         <v>1</v>
       </c>
       <c r="EK14" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EL14" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM14">
         <v>96</v>
       </c>
       <c r="EN14" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO14">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="EP14" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EQ14">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="ER14">
         <v>0</v>
@@ -9714,10 +9681,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F15" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G15" t="b">
         <v>0</v>
@@ -9753,10 +9720,10 @@
         <v>1</v>
       </c>
       <c r="R15">
-        <v>945000</v>
+        <v>2012000</v>
       </c>
       <c r="S15" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="T15" t="s">
         <v>162</v>
@@ -9804,7 +9771,7 @@
         <v>15000000</v>
       </c>
       <c r="AL15" t="s">
-        <v>166</v>
+        <v>225</v>
       </c>
       <c r="AM15">
         <v>55</v>
@@ -9834,10 +9801,10 @@
         <v>1</v>
       </c>
       <c r="AV15">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="AW15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AX15">
         <v>55</v>
@@ -9867,7 +9834,7 @@
         <v>1</v>
       </c>
       <c r="BL15" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BM15">
         <v>2</v>
@@ -9876,7 +9843,7 @@
         <v>9</v>
       </c>
       <c r="BO15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BP15">
         <v>0</v>
@@ -9888,7 +9855,7 @@
         <v>1</v>
       </c>
       <c r="BV15" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="BW15">
         <v>2</v>
@@ -9897,7 +9864,7 @@
         <v>9</v>
       </c>
       <c r="BY15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BZ15">
         <v>0</v>
@@ -9909,7 +9876,7 @@
         <v>1</v>
       </c>
       <c r="CF15" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CG15">
         <v>2</v>
@@ -9918,7 +9885,7 @@
         <v>9</v>
       </c>
       <c r="CI15" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CJ15">
         <v>0</v>
@@ -9930,7 +9897,7 @@
         <v>1</v>
       </c>
       <c r="CO15" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CP15">
         <v>0</v>
@@ -9942,7 +9909,7 @@
         <v>1</v>
       </c>
       <c r="DM15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="DN15">
         <v>0.05</v>
@@ -9957,10 +9924,10 @@
         <v>8</v>
       </c>
       <c r="DR15" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS15" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DT15">
         <v>0</v>
@@ -9972,7 +9939,7 @@
         <v>1</v>
       </c>
       <c r="EC15" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="ED15">
         <v>0</v>
@@ -9984,25 +9951,25 @@
         <v>1</v>
       </c>
       <c r="EK15" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EL15" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM15">
         <v>96</v>
       </c>
       <c r="EN15" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO15">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="EP15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EQ15">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="ER15">
         <v>0</v>
@@ -10019,10 +9986,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F16" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G16" t="b">
         <v>0</v>
@@ -10058,10 +10025,10 @@
         <v>1</v>
       </c>
       <c r="R16">
-        <v>2012000</v>
+        <v>2455000</v>
       </c>
       <c r="S16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="T16" t="s">
         <v>162</v>
@@ -10109,7 +10076,7 @@
         <v>15000000</v>
       </c>
       <c r="AL16" t="s">
-        <v>164</v>
+        <v>225</v>
       </c>
       <c r="AM16">
         <v>55</v>
@@ -10142,7 +10109,7 @@
         <v>3200</v>
       </c>
       <c r="AW16" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="AX16">
         <v>55</v>
@@ -10172,7 +10139,7 @@
         <v>1</v>
       </c>
       <c r="BL16" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BM16">
         <v>2</v>
@@ -10181,7 +10148,7 @@
         <v>9</v>
       </c>
       <c r="BO16" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BP16">
         <v>0</v>
@@ -10193,7 +10160,7 @@
         <v>1</v>
       </c>
       <c r="BV16" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="BW16">
         <v>2</v>
@@ -10202,7 +10169,7 @@
         <v>9</v>
       </c>
       <c r="BY16" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BZ16">
         <v>0</v>
@@ -10214,7 +10181,7 @@
         <v>1</v>
       </c>
       <c r="CF16" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CG16">
         <v>2</v>
@@ -10223,7 +10190,7 @@
         <v>9</v>
       </c>
       <c r="CI16" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CJ16">
         <v>0</v>
@@ -10235,7 +10202,7 @@
         <v>1</v>
       </c>
       <c r="CO16" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CP16">
         <v>0</v>
@@ -10247,7 +10214,7 @@
         <v>1</v>
       </c>
       <c r="DM16" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="DN16">
         <v>0.05</v>
@@ -10262,10 +10229,10 @@
         <v>8</v>
       </c>
       <c r="DR16" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS16" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DT16">
         <v>0</v>
@@ -10277,7 +10244,7 @@
         <v>1</v>
       </c>
       <c r="EC16" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="ED16">
         <v>0</v>
@@ -10289,25 +10256,25 @@
         <v>1</v>
       </c>
       <c r="EK16" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EL16" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM16">
         <v>96</v>
       </c>
       <c r="EN16" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO16">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="EP16" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EQ16">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="ER16">
         <v>0</v>
@@ -10324,10 +10291,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F17" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G17" t="b">
         <v>0</v>
@@ -10363,10 +10330,10 @@
         <v>1</v>
       </c>
       <c r="R17">
-        <v>1720000</v>
+        <v>1158000</v>
       </c>
       <c r="S17" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="T17" t="s">
         <v>162</v>
@@ -10414,7 +10381,7 @@
         <v>15000000</v>
       </c>
       <c r="AL17" t="s">
-        <v>222</v>
+        <v>164</v>
       </c>
       <c r="AM17">
         <v>35</v>
@@ -10444,10 +10411,10 @@
         <v>1</v>
       </c>
       <c r="AV17">
-        <v>2800</v>
+        <v>3200</v>
       </c>
       <c r="AW17" t="s">
-        <v>224</v>
+        <v>175</v>
       </c>
       <c r="AX17">
         <v>55</v>
@@ -10477,7 +10444,7 @@
         <v>1</v>
       </c>
       <c r="BL17" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BM17">
         <v>2</v>
@@ -10486,7 +10453,7 @@
         <v>9</v>
       </c>
       <c r="BO17" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BP17">
         <v>0</v>
@@ -10498,7 +10465,7 @@
         <v>1</v>
       </c>
       <c r="BV17" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="BW17">
         <v>2</v>
@@ -10507,7 +10474,7 @@
         <v>9</v>
       </c>
       <c r="BY17" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BZ17">
         <v>0</v>
@@ -10519,7 +10486,7 @@
         <v>1</v>
       </c>
       <c r="CF17" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="CG17">
         <v>2</v>
@@ -10528,7 +10495,7 @@
         <v>9</v>
       </c>
       <c r="CI17" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CJ17">
         <v>0</v>
@@ -10540,7 +10507,7 @@
         <v>1</v>
       </c>
       <c r="CO17" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CP17">
         <v>1</v>
@@ -10552,7 +10519,7 @@
         <v>1</v>
       </c>
       <c r="CS17" t="s">
-        <v>185</v>
+        <v>232</v>
       </c>
       <c r="CT17">
         <v>75000</v>
@@ -10582,22 +10549,22 @@
         <v>0</v>
       </c>
       <c r="DC17" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="DD17">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="DE17">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="DF17">
         <v>7200</v>
       </c>
       <c r="DG17">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="DH17">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="DI17">
         <v>0.9</v>
@@ -10627,10 +10594,10 @@
         <v>8</v>
       </c>
       <c r="DR17" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="DS17" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="DT17">
         <v>0</v>
@@ -10642,7 +10609,7 @@
         <v>1</v>
       </c>
       <c r="EC17" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="ED17">
         <v>0</v>
@@ -10654,22 +10621,22 @@
         <v>1</v>
       </c>
       <c r="EK17" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="EL17" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="EM17">
         <v>96</v>
       </c>
       <c r="EN17" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="EO17">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="EP17" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EQ17">
         <v>0</v>
@@ -10708,13 +10675,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>9</v>
@@ -10995,13 +10962,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G2">
-        <v>543</v>
+        <v>237</v>
       </c>
       <c r="H2">
         <v>96</v>
@@ -11019,10 +10986,10 @@
         <v>1</v>
       </c>
       <c r="M2">
-        <v>15120000</v>
+        <v>9170000</v>
       </c>
       <c r="N2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O2" t="s">
         <v>162</v>
@@ -11046,7 +11013,7 @@
         <v>1</v>
       </c>
       <c r="W2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Y2" t="s">
         <v>162</v>
@@ -11070,22 +11037,22 @@
         <v>1</v>
       </c>
       <c r="AF2">
-        <v>8630000</v>
+        <v>4320000</v>
       </c>
       <c r="AG2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AI2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AJ2" t="b">
         <v>1</v>
       </c>
       <c r="AK2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AL2">
         <v>2</v>
@@ -11094,7 +11061,7 @@
         <v>9</v>
       </c>
       <c r="AN2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AO2">
         <v>0</v>
@@ -11106,7 +11073,7 @@
         <v>1</v>
       </c>
       <c r="AU2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="AV2">
         <v>2</v>
@@ -11115,7 +11082,7 @@
         <v>9</v>
       </c>
       <c r="AX2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AY2">
         <v>0</v>
@@ -11127,7 +11094,7 @@
         <v>1</v>
       </c>
       <c r="BE2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BF2">
         <v>2</v>
@@ -11136,7 +11103,7 @@
         <v>9</v>
       </c>
       <c r="BH2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="BI2">
         <v>0</v>
@@ -11148,10 +11115,10 @@
         <v>1</v>
       </c>
       <c r="CA2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="CB2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CC2">
         <v>1</v>
@@ -11160,13 +11127,13 @@
         <v>1</v>
       </c>
       <c r="CE2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="CF2">
-        <v>15100</v>
+        <v>9200</v>
       </c>
       <c r="CG2">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="CH2">
         <v>0.95</v>
@@ -11181,25 +11148,25 @@
         <v>0</v>
       </c>
       <c r="CL2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CM2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="CN2">
         <v>96</v>
       </c>
       <c r="CO2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="CP2">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="CQ2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="CR2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CS2">
         <v>0</v>
@@ -11216,13 +11183,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G3">
-        <v>184</v>
+        <v>535</v>
       </c>
       <c r="H3">
         <v>96</v>
@@ -11240,10 +11207,10 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <v>6850000</v>
+        <v>14610000</v>
       </c>
       <c r="N3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O3" t="s">
         <v>162</v>
@@ -11267,7 +11234,7 @@
         <v>1</v>
       </c>
       <c r="W3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Y3" t="s">
         <v>162</v>
@@ -11282,31 +11249,16 @@
         <v>163</v>
       </c>
       <c r="AC3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>1</v>
       </c>
-      <c r="AF3">
-        <v>3260000</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>248</v>
-      </c>
-      <c r="AH3">
-        <v>-20</v>
-      </c>
-      <c r="AI3">
-        <v>50</v>
-      </c>
-      <c r="AJ3" t="b">
-        <v>1</v>
-      </c>
       <c r="AK3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AL3">
         <v>2</v>
@@ -11315,7 +11267,7 @@
         <v>9</v>
       </c>
       <c r="AN3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AO3">
         <v>0</v>
@@ -11327,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="AU3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="AV3">
         <v>2</v>
@@ -11336,7 +11288,7 @@
         <v>9</v>
       </c>
       <c r="AX3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AY3">
         <v>0</v>
@@ -11348,7 +11300,7 @@
         <v>1</v>
       </c>
       <c r="BE3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BF3">
         <v>2</v>
@@ -11357,115 +11309,52 @@
         <v>9</v>
       </c>
       <c r="BH3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="BI3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="b">
         <v>1</v>
       </c>
-      <c r="BL3" t="s">
-        <v>183</v>
-      </c>
-      <c r="BM3">
-        <v>75000</v>
-      </c>
-      <c r="BN3">
-        <v>25000</v>
-      </c>
-      <c r="BO3">
-        <v>11000</v>
-      </c>
-      <c r="BP3">
-        <v>22000</v>
-      </c>
-      <c r="BQ3">
-        <v>200000</v>
-      </c>
-      <c r="BR3">
-        <v>0.9</v>
-      </c>
-      <c r="BS3">
-        <v>0.8</v>
-      </c>
-      <c r="BT3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BU3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>188</v>
-      </c>
-      <c r="BW3">
-        <v>0.05</v>
-      </c>
-      <c r="BX3">
-        <v>0.5</v>
-      </c>
-      <c r="BY3">
-        <v>0.8</v>
-      </c>
-      <c r="BZ3">
-        <v>8</v>
-      </c>
       <c r="CA3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="CB3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CC3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE3" t="s">
-        <v>190</v>
-      </c>
-      <c r="CF3">
-        <v>6800</v>
-      </c>
-      <c r="CG3">
-        <v>14000</v>
-      </c>
-      <c r="CH3">
-        <v>0.95</v>
-      </c>
-      <c r="CI3">
-        <v>0.1</v>
-      </c>
-      <c r="CJ3" t="b">
-        <v>0</v>
-      </c>
-      <c r="CK3" t="b">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="CL3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CM3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="CN3">
         <v>96</v>
       </c>
       <c r="CO3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="CP3">
         <v>48</v>
       </c>
       <c r="CQ3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="CR3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="CS3">
         <v>0</v>
@@ -11482,13 +11371,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G4">
-        <v>526</v>
+        <v>187</v>
       </c>
       <c r="H4">
         <v>96</v>
@@ -11506,10 +11395,10 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>15360000</v>
+        <v>6740000</v>
       </c>
       <c r="N4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O4" t="s">
         <v>162</v>
@@ -11533,7 +11422,7 @@
         <v>1</v>
       </c>
       <c r="W4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Y4" t="s">
         <v>162</v>
@@ -11548,16 +11437,31 @@
         <v>163</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="b">
         <v>1</v>
       </c>
+      <c r="AF4">
+        <v>3900000</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>229</v>
+      </c>
+      <c r="AH4">
+        <v>-20</v>
+      </c>
+      <c r="AI4">
+        <v>50</v>
+      </c>
+      <c r="AJ4" t="b">
+        <v>1</v>
+      </c>
       <c r="AK4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AL4">
         <v>2</v>
@@ -11566,7 +11470,7 @@
         <v>9</v>
       </c>
       <c r="AN4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AO4">
         <v>0</v>
@@ -11578,7 +11482,7 @@
         <v>1</v>
       </c>
       <c r="AU4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="AV4">
         <v>2</v>
@@ -11587,7 +11491,7 @@
         <v>9</v>
       </c>
       <c r="AX4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AY4">
         <v>0</v>
@@ -11599,7 +11503,7 @@
         <v>1</v>
       </c>
       <c r="BE4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BF4">
         <v>2</v>
@@ -11608,7 +11512,7 @@
         <v>9</v>
       </c>
       <c r="BH4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="BI4">
         <v>0</v>
@@ -11620,40 +11524,58 @@
         <v>1</v>
       </c>
       <c r="CA4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="CB4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CC4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE4" t="s">
-        <v>190</v>
+        <v>194</v>
+      </c>
+      <c r="CF4">
+        <v>6700</v>
+      </c>
+      <c r="CG4">
+        <v>13000</v>
+      </c>
+      <c r="CH4">
+        <v>0.95</v>
+      </c>
+      <c r="CI4">
+        <v>0.1</v>
+      </c>
+      <c r="CJ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK4" t="b">
+        <v>0</v>
       </c>
       <c r="CL4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CM4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="CN4">
         <v>96</v>
       </c>
       <c r="CO4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="CP4">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="CQ4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="CR4">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="CS4">
         <v>0</v>
@@ -11670,13 +11592,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G5">
-        <v>192</v>
+        <v>517</v>
       </c>
       <c r="H5">
         <v>96</v>
@@ -11694,10 +11616,10 @@
         <v>1</v>
       </c>
       <c r="M5">
-        <v>7730000</v>
+        <v>16800000</v>
       </c>
       <c r="N5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O5" t="s">
         <v>162</v>
@@ -11721,7 +11643,7 @@
         <v>1</v>
       </c>
       <c r="W5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Y5" t="s">
         <v>162</v>
@@ -11736,31 +11658,16 @@
         <v>163</v>
       </c>
       <c r="AC5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>1</v>
       </c>
-      <c r="AF5">
-        <v>4380000</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>226</v>
-      </c>
-      <c r="AH5">
-        <v>-20</v>
-      </c>
-      <c r="AI5">
-        <v>50</v>
-      </c>
-      <c r="AJ5" t="b">
-        <v>1</v>
-      </c>
       <c r="AK5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AL5">
         <v>2</v>
@@ -11769,7 +11676,7 @@
         <v>9</v>
       </c>
       <c r="AN5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AO5">
         <v>0</v>
@@ -11781,7 +11688,7 @@
         <v>1</v>
       </c>
       <c r="AU5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="AV5">
         <v>2</v>
@@ -11790,7 +11697,7 @@
         <v>9</v>
       </c>
       <c r="AX5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AY5">
         <v>0</v>
@@ -11802,7 +11709,7 @@
         <v>1</v>
       </c>
       <c r="BE5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BF5">
         <v>2</v>
@@ -11811,7 +11718,7 @@
         <v>9</v>
       </c>
       <c r="BH5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="BI5">
         <v>0</v>
@@ -11823,58 +11730,40 @@
         <v>1</v>
       </c>
       <c r="CA5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="CB5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CC5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE5" t="s">
-        <v>190</v>
-      </c>
-      <c r="CF5">
-        <v>7700</v>
-      </c>
-      <c r="CG5">
-        <v>15000</v>
-      </c>
-      <c r="CH5">
-        <v>0.95</v>
-      </c>
-      <c r="CI5">
-        <v>0.1</v>
-      </c>
-      <c r="CJ5" t="b">
-        <v>0</v>
-      </c>
-      <c r="CK5" t="b">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="CL5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CM5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="CN5">
         <v>96</v>
       </c>
       <c r="CO5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="CP5">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="CQ5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="CR5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CS5">
         <v>0</v>
@@ -11910,13 +11799,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>9</v>
@@ -12233,7 +12122,7 @@
         <v>251</v>
       </c>
       <c r="G2">
-        <v>2135</v>
+        <v>4944</v>
       </c>
       <c r="H2">
         <v>96</v>
@@ -12251,7 +12140,7 @@
         <v>1</v>
       </c>
       <c r="M2">
-        <v>1002000000</v>
+        <v>1155100000</v>
       </c>
       <c r="N2" t="s">
         <v>253</v>
@@ -12302,22 +12191,22 @@
         <v>1</v>
       </c>
       <c r="AF2">
-        <v>1229000000</v>
+        <v>1641000000</v>
       </c>
       <c r="AG2" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="AH2">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AJ2" t="b">
         <v>1</v>
       </c>
       <c r="AK2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AL2">
         <v>2</v>
@@ -12326,28 +12215,19 @@
         <v>9</v>
       </c>
       <c r="AN2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AO2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="b">
         <v>1</v>
       </c>
-      <c r="AR2">
-        <v>104300000</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>255</v>
-      </c>
-      <c r="AT2" t="b">
-        <v>1</v>
-      </c>
       <c r="AU2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="AV2">
         <v>2</v>
@@ -12356,7 +12236,7 @@
         <v>9</v>
       </c>
       <c r="AX2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AY2">
         <v>0</v>
@@ -12368,7 +12248,7 @@
         <v>1</v>
       </c>
       <c r="BE2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BF2">
         <v>2</v>
@@ -12377,97 +12257,22 @@
         <v>9</v>
       </c>
       <c r="BH2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="BI2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="b">
         <v>1</v>
       </c>
-      <c r="BL2" t="s">
-        <v>229</v>
-      </c>
-      <c r="BM2">
-        <v>750000</v>
-      </c>
-      <c r="BN2">
-        <v>25000</v>
-      </c>
-      <c r="BO2">
-        <v>11000</v>
-      </c>
-      <c r="BP2">
-        <v>22000</v>
-      </c>
-      <c r="BQ2">
-        <v>200000</v>
-      </c>
-      <c r="BR2">
-        <v>0.9</v>
-      </c>
-      <c r="BS2">
-        <v>0.8</v>
-      </c>
-      <c r="BT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BV2" t="s">
-        <v>186</v>
-      </c>
-      <c r="BW2">
-        <v>750000</v>
-      </c>
-      <c r="BX2">
-        <v>25000</v>
-      </c>
-      <c r="BY2">
-        <v>11000</v>
-      </c>
-      <c r="BZ2">
-        <v>22000</v>
-      </c>
-      <c r="CA2">
-        <v>200000</v>
-      </c>
-      <c r="CB2">
-        <v>0.9</v>
-      </c>
-      <c r="CC2">
-        <v>0.8</v>
-      </c>
-      <c r="CD2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CF2" t="s">
-        <v>188</v>
-      </c>
-      <c r="CG2">
-        <v>0.05</v>
-      </c>
-      <c r="CH2">
-        <v>0.5</v>
-      </c>
-      <c r="CI2">
-        <v>0.8</v>
-      </c>
-      <c r="CJ2">
-        <v>8</v>
-      </c>
       <c r="CK2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="CL2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CM2">
         <v>0</v>
@@ -12476,28 +12281,28 @@
         <v>0</v>
       </c>
       <c r="CO2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="CV2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CW2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="CX2">
         <v>96</v>
       </c>
       <c r="CY2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="CZ2">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="DA2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="DB2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="DC2">
         <v>0</v>
@@ -12520,7 +12325,7 @@
         <v>252</v>
       </c>
       <c r="G3">
-        <v>4819</v>
+        <v>2052</v>
       </c>
       <c r="H3">
         <v>96</v>
@@ -12538,7 +12343,7 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <v>1211000000</v>
+        <v>840800000</v>
       </c>
       <c r="N3" t="s">
         <v>254</v>
@@ -12589,7 +12394,7 @@
         <v>1</v>
       </c>
       <c r="AK3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AL3">
         <v>2</v>
@@ -12598,19 +12403,28 @@
         <v>9</v>
       </c>
       <c r="AN3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AO3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="b">
         <v>1</v>
       </c>
+      <c r="AR3">
+        <v>78440000</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>184</v>
+      </c>
+      <c r="AT3" t="b">
+        <v>1</v>
+      </c>
       <c r="AU3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="AV3">
         <v>2</v>
@@ -12619,7 +12433,7 @@
         <v>9</v>
       </c>
       <c r="AX3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AY3">
         <v>0</v>
@@ -12631,7 +12445,7 @@
         <v>1</v>
       </c>
       <c r="BE3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BF3">
         <v>2</v>
@@ -12640,67 +12454,22 @@
         <v>9</v>
       </c>
       <c r="BH3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="BI3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="b">
         <v>1</v>
       </c>
-      <c r="BL3" t="s">
-        <v>185</v>
-      </c>
-      <c r="BM3">
-        <v>500000</v>
-      </c>
-      <c r="BN3">
-        <v>20000</v>
-      </c>
-      <c r="BO3">
-        <v>7200</v>
-      </c>
-      <c r="BP3">
-        <v>11000</v>
-      </c>
-      <c r="BQ3">
-        <v>100000</v>
-      </c>
-      <c r="BR3">
-        <v>0.9</v>
-      </c>
-      <c r="BS3">
-        <v>0.8</v>
-      </c>
-      <c r="BT3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BU3" t="b">
-        <v>0</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>256</v>
-      </c>
-      <c r="CG3">
-        <v>0.05</v>
-      </c>
-      <c r="CH3">
-        <v>0.5</v>
-      </c>
-      <c r="CI3">
-        <v>0.8</v>
-      </c>
-      <c r="CJ3">
-        <v>8</v>
-      </c>
       <c r="CK3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="CL3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CM3">
         <v>0</v>
@@ -12709,25 +12478,25 @@
         <v>0</v>
       </c>
       <c r="CO3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="CV3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="CW3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="CX3">
         <v>96</v>
       </c>
       <c r="CY3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="CZ3">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="DA3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="DB3">
         <v>0</v>
@@ -12766,7 +12535,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>9</v>
@@ -12924,7 +12693,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F2">
         <v>96</v>
@@ -12942,10 +12711,10 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>32100000</v>
+        <v>39800000</v>
       </c>
       <c r="L2" t="s">
-        <v>227</v>
+        <v>255</v>
       </c>
       <c r="M2">
         <v>-20</v>
@@ -12957,7 +12726,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -12966,7 +12735,7 @@
         <v>9</v>
       </c>
       <c r="S2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AN2">
         <v>1</v>
@@ -12978,10 +12747,10 @@
         <v>1</v>
       </c>
       <c r="AQ2">
-        <v>16050000</v>
+        <v>19900000</v>
       </c>
       <c r="AR2">
-        <v>32100000</v>
+        <v>39800000</v>
       </c>
       <c r="AS2">
         <v>0.95</v>
@@ -12996,19 +12765,19 @@
         <v>1</v>
       </c>
       <c r="AW2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AX2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AY2">
         <v>96</v>
       </c>
       <c r="AZ2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="BA2">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="BB2">
         <v>0</v>
@@ -13025,7 +12794,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F3">
         <v>96</v>
@@ -13043,10 +12812,10 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>14000000</v>
+        <v>18300000</v>
       </c>
       <c r="L3" t="s">
-        <v>227</v>
+        <v>255</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -13058,7 +12827,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q3">
         <v>2</v>
@@ -13067,7 +12836,7 @@
         <v>9</v>
       </c>
       <c r="S3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AN3">
         <v>1</v>
@@ -13079,10 +12848,10 @@
         <v>1</v>
       </c>
       <c r="AQ3">
-        <v>7000000</v>
+        <v>9150000</v>
       </c>
       <c r="AR3">
-        <v>14000000</v>
+        <v>18300000</v>
       </c>
       <c r="AS3">
         <v>0.95</v>
@@ -13097,19 +12866,19 @@
         <v>1</v>
       </c>
       <c r="AW3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AX3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AY3">
         <v>96</v>
       </c>
       <c r="AZ3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="BA3">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="BB3">
         <v>0</v>
@@ -13126,7 +12895,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F4">
         <v>96</v>
@@ -13144,22 +12913,22 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>59800000</v>
+        <v>17200000</v>
       </c>
       <c r="L4" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="M4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="O4">
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q4">
         <v>2</v>
@@ -13168,7 +12937,7 @@
         <v>9</v>
       </c>
       <c r="S4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AN4">
         <v>1</v>
@@ -13180,10 +12949,10 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>29900000</v>
+        <v>8600000</v>
       </c>
       <c r="AR4">
-        <v>59800000</v>
+        <v>17200000</v>
       </c>
       <c r="AS4">
         <v>0.95</v>
@@ -13198,19 +12967,19 @@
         <v>1</v>
       </c>
       <c r="AW4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AX4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AY4">
         <v>96</v>
       </c>
       <c r="AZ4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="BA4">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="BB4">
         <v>0</v>
@@ -13227,7 +12996,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F5">
         <v>96</v>
@@ -13245,22 +13014,22 @@
         <v>1</v>
       </c>
       <c r="K5">
-        <v>15500000</v>
+        <v>62600000</v>
       </c>
       <c r="L5" t="s">
-        <v>226</v>
+        <v>255</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="O5">
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q5">
         <v>2</v>
@@ -13269,7 +13038,7 @@
         <v>9</v>
       </c>
       <c r="S5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AN5">
         <v>1</v>
@@ -13281,10 +13050,10 @@
         <v>1</v>
       </c>
       <c r="AQ5">
-        <v>7750000</v>
+        <v>31300000</v>
       </c>
       <c r="AR5">
-        <v>15500000</v>
+        <v>62600000</v>
       </c>
       <c r="AS5">
         <v>0.95</v>
@@ -13299,19 +13068,19 @@
         <v>1</v>
       </c>
       <c r="AW5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AX5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AY5">
         <v>96</v>
       </c>
       <c r="AZ5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="BA5">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="BB5">
         <v>0</v>
@@ -13328,7 +13097,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F6">
         <v>96</v>
@@ -13346,16 +13115,16 @@
         <v>1</v>
       </c>
       <c r="AG6">
-        <v>20000</v>
+        <v>39600</v>
       </c>
       <c r="AH6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AI6" t="b">
         <v>1</v>
       </c>
       <c r="AJ6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AK6">
         <v>2</v>
@@ -13364,7 +13133,7 @@
         <v>9</v>
       </c>
       <c r="AM6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AN6">
         <v>0</v>
@@ -13376,19 +13145,19 @@
         <v>1</v>
       </c>
       <c r="AW6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AX6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AY6">
         <v>96</v>
       </c>
       <c r="AZ6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="BA6">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BB6">
         <v>0</v>
@@ -13405,7 +13174,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F7">
         <v>96</v>
@@ -13423,16 +13192,16 @@
         <v>1</v>
       </c>
       <c r="AG7">
-        <v>38100</v>
+        <v>20000</v>
       </c>
       <c r="AH7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AI7" t="b">
         <v>1</v>
       </c>
       <c r="AJ7" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AK7">
         <v>2</v>
@@ -13441,31 +13210,49 @@
         <v>9</v>
       </c>
       <c r="AM7" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP7" t="b">
         <v>1</v>
       </c>
+      <c r="AQ7">
+        <v>6000</v>
+      </c>
+      <c r="AR7">
+        <v>20000</v>
+      </c>
+      <c r="AS7">
+        <v>0.95</v>
+      </c>
+      <c r="AT7">
+        <v>0.1</v>
+      </c>
+      <c r="AU7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="b">
+        <v>1</v>
+      </c>
       <c r="AW7" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AX7" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AY7">
         <v>96</v>
       </c>
       <c r="AZ7" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="BA7">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="BB7">
         <v>0</v>
@@ -13501,7 +13288,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>9</v>
@@ -13537,64 +13324,64 @@
         <v>128</v>
       </c>
       <c r="R1" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>282</v>
       </c>
       <c r="AL1" s="1" t="s">
         <v>137</v>
@@ -13623,7 +13410,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F2">
         <v>96</v>
@@ -13641,10 +13428,10 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>852000</v>
+        <v>2378000</v>
       </c>
       <c r="L2">
-        <v>5380000</v>
+        <v>8000000</v>
       </c>
       <c r="M2">
         <v>0.95</v>
@@ -13659,19 +13446,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AL2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AM2">
         <v>96</v>
       </c>
       <c r="AN2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AO2">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="AP2">
         <v>0</v>
@@ -13688,7 +13475,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F3">
         <v>96</v>
@@ -13706,10 +13493,10 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>1056000</v>
+        <v>1033000</v>
       </c>
       <c r="L3">
-        <v>4310000</v>
+        <v>5980000</v>
       </c>
       <c r="M3">
         <v>0.95</v>
@@ -13724,19 +13511,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AL3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AM3">
         <v>96</v>
       </c>
       <c r="AN3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AO3">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="AP3">
         <v>0</v>
@@ -13753,7 +13540,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F4">
         <v>96</v>
@@ -13771,10 +13558,10 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>1875000</v>
+        <v>823000</v>
       </c>
       <c r="L4">
-        <v>8240000</v>
+        <v>5900000</v>
       </c>
       <c r="M4">
         <v>0.95</v>
@@ -13789,19 +13576,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AL4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AM4">
         <v>96</v>
       </c>
       <c r="AN4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AO4">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="AP4">
         <v>0</v>
@@ -13818,7 +13605,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F5">
         <v>96</v>
@@ -13836,10 +13623,10 @@
         <v>1</v>
       </c>
       <c r="U5">
-        <v>2150000000</v>
+        <v>1090000000</v>
       </c>
       <c r="V5">
-        <v>9790000000</v>
+        <v>4440000000</v>
       </c>
       <c r="W5">
         <v>0.95</v>
@@ -13854,19 +13641,19 @@
         <v>1</v>
       </c>
       <c r="AA5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AL5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AM5">
         <v>96</v>
       </c>
       <c r="AN5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AO5">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="AP5">
         <v>0</v>
@@ -13883,7 +13670,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F6">
         <v>96</v>
@@ -13901,10 +13688,10 @@
         <v>1</v>
       </c>
       <c r="U6">
-        <v>1150000000</v>
+        <v>1620000000</v>
       </c>
       <c r="V6">
-        <v>5090000000</v>
+        <v>7880000000</v>
       </c>
       <c r="W6">
         <v>0.95</v>
@@ -13919,19 +13706,19 @@
         <v>1</v>
       </c>
       <c r="AA6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AL6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AM6">
         <v>96</v>
       </c>
       <c r="AN6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AO6">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AP6">
         <v>0</v>
@@ -13948,7 +13735,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F7">
         <v>96</v>
@@ -13966,10 +13753,10 @@
         <v>1</v>
       </c>
       <c r="U7">
-        <v>1160000000</v>
+        <v>1030000000</v>
       </c>
       <c r="V7">
-        <v>4320000000</v>
+        <v>4050000000</v>
       </c>
       <c r="W7">
         <v>0.95</v>
@@ -13984,19 +13771,19 @@
         <v>1</v>
       </c>
       <c r="AA7" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AL7" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AM7">
         <v>96</v>
       </c>
       <c r="AN7" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AO7">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AP7">
         <v>0</v>
@@ -14013,7 +13800,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F8">
         <v>96</v>
@@ -14031,10 +13818,10 @@
         <v>1</v>
       </c>
       <c r="AE8">
-        <v>201100000</v>
+        <v>207900000</v>
       </c>
       <c r="AF8">
-        <v>668000000</v>
+        <v>683000000</v>
       </c>
       <c r="AG8">
         <v>0.95</v>
@@ -14049,19 +13836,19 @@
         <v>1</v>
       </c>
       <c r="AK8" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AL8" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AM8">
         <v>96</v>
       </c>
       <c r="AN8" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AO8">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AP8">
         <v>0</v>
@@ -14078,7 +13865,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F9">
         <v>96</v>
@@ -14096,10 +13883,10 @@
         <v>1</v>
       </c>
       <c r="AE9">
-        <v>90500000</v>
+        <v>84000000</v>
       </c>
       <c r="AF9">
-        <v>476000000</v>
+        <v>430000000</v>
       </c>
       <c r="AG9">
         <v>0.95</v>
@@ -14114,19 +13901,19 @@
         <v>1</v>
       </c>
       <c r="AK9" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AL9" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AM9">
         <v>96</v>
       </c>
       <c r="AN9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AO9">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AP9">
         <v>0</v>
@@ -14143,7 +13930,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F10">
         <v>96</v>
@@ -14161,10 +13948,10 @@
         <v>1</v>
       </c>
       <c r="AE10">
-        <v>94300000</v>
+        <v>85500000</v>
       </c>
       <c r="AF10">
-        <v>561000000</v>
+        <v>482000000</v>
       </c>
       <c r="AG10">
         <v>0.95</v>
@@ -14179,19 +13966,19 @@
         <v>1</v>
       </c>
       <c r="AK10" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AL10" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AM10">
         <v>96</v>
       </c>
       <c r="AN10" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AO10">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AP10">
         <v>0</v>
